--- a/entregables/TCNB_calibracion_series.xlsx
+++ b/entregables/TCNB_calibracion_series.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A38"/>
+  <dimension ref="A1:A40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -639,105 +639,119 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">   BetaCal   a = 1.714773   b = -1.240160   m = 1.804671</t>
+          <t xml:space="preserve">   BetaCal   a = 1.472959   b = 0.000000   m = 1.094112</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   corrimiento probit = -0.271454     delta_0 = +0.182368</t>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ajustada con la restriccion monotona del pipeline (a&gt;=0, b&gt;=0). Sin ella el</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ajuste global da b&lt;0 y la PD calibrada decrece por encima de 58% de PD cruda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   corrimiento probit = -0.271976     delta_0 = +0.182368</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   rho = 0.0332     lambda = 1.0     LRA = 6.9834%</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>PROYECCION DE LA MORA</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Los meses sin mora 12m cerrada se proyectan por chain-ladder: se toma el ultimo</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>horizonte con dato y se multiplica por el factor h-&gt;12 de la propia hoja.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>V1, V2 y V3 son el P25, la mediana y el P75 de los factores historicos, y solo</t>
+          <t>Los meses sin mora 12m cerrada se proyectan por chain-ladder: se toma el ultimo</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
+          <t>horizonte con dato y se multiplica por el factor h-&gt;12 de la propia hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>V1, V2 y V3 son el P25, la mediana y el P75 de los factores historicos, y solo</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
           <t>se calculan en las hojas de IBK.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>COLUMNAS CALCULADAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>EC vigente        PD cal vigente / mora 12m  - 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>EC NUEVA          PD cal NUEVA   / mora 12m  - 1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>EC NUEVA vs proy  PD cal NUEVA   / proy      - 1   (para los meses sin mora cerrada)</t>
+          <t>EC vigente        PD cal vigente / mora 12m  - 1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
+          <t>EC NUEVA          PD cal NUEVA   / mora 12m  - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>EC NUEVA vs proy  PD cal NUEVA   / proy      - 1   (para los meses sin mora cerrada)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
           <t>Son formulas vivas: si se edita una celda de entrada, el error se recalcula.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Generado por Programas/reportes/10_excel_series.py</t>
         </is>
@@ -935,7 +949,7 @@
         <v>0.1660379595796832</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>0.1391144776947785</v>
+        <v>0.1375568991854284</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>0.007111597374179431</v>
@@ -1014,7 +1028,7 @@
         <v>0.1664079985963771</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.1393467996187831</v>
+        <v>0.1378731848332384</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>0.00471342383107089</v>
@@ -1093,7 +1107,7 @@
         <v>0.1629954402597873</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.1359711128293958</v>
+        <v>0.1345153431147133</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0.006322668250869897</v>
@@ -1172,7 +1186,7 @@
         <v>0.1578369241884913</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.1306467043321142</v>
+        <v>0.1294873717460337</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>0.006436179301703025</v>
@@ -1251,7 +1265,7 @@
         <v>0.1233364785159737</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.1228738970872642</v>
+        <v>0.122226938082706</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>0.003405704555129843</v>
@@ -1330,7 +1344,7 @@
         <v>0.1244268395551793</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.1244300878007985</v>
+        <v>0.1234328437425222</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>0.00411775551594862</v>
@@ -1409,7 +1423,7 @@
         <v>0.1156866766943294</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>0.1199028997260603</v>
+        <v>0.118857558833138</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>0.003478765038411364</v>
@@ -1488,7 +1502,7 @@
         <v>0.1228169047329705</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0.1147429272938872</v>
+        <v>0.1137794656282025</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>0.003286713286713287</v>
@@ -1567,7 +1581,7 @@
         <v>0.1298233347756259</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>0.1164331749286055</v>
+        <v>0.1154754444868372</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>0.003275681341719077</v>
@@ -1646,7 +1660,7 @@
         <v>0.1356364520438287</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>0.1200368243554048</v>
+        <v>0.1191038044872064</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>0.005481042042816611</v>
@@ -1725,7 +1739,7 @@
         <v>0.1237410325682142</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>0.1121671808645059</v>
+        <v>0.1111886346644216</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>0.004803022126281705</v>
@@ -1804,7 +1818,7 @@
         <v>0.1249736210942026</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.1132544981012731</v>
+        <v>0.1123403471016208</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>0.006160277212474561</v>
@@ -1883,7 +1897,7 @@
         <v>0.1167956862047136</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>0.102567625451396</v>
+        <v>0.1016809175837778</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>0.007068771883464359</v>
@@ -1962,7 +1976,7 @@
         <v>0.1249974336716362</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0.1062440485876536</v>
+        <v>0.1053416320970148</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>0.004077471967380225</v>
@@ -2041,7 +2055,7 @@
         <v>0.1241018679046092</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>0.1020308751102681</v>
+        <v>0.1013379192186528</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>0.003747148908439231</v>
@@ -2120,7 +2134,7 @@
         <v>0.1250648298912176</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>0.1048513031751253</v>
+        <v>0.1038285943001639</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>0.003209098074541155</v>
@@ -2199,7 +2213,7 @@
         <v>0.1284710042879902</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>0.107381432821319</v>
+        <v>0.1065765311385731</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>0.003864214439444336</v>
@@ -2278,7 +2292,7 @@
         <v>0.1273795809788002</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.1057012372639873</v>
+        <v>0.1048427403491569</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>0.003375663076675776</v>
@@ -2357,7 +2371,7 @@
         <v>0.1306935973794915</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>0.107631757242308</v>
+        <v>0.1070131687968914</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>0.003468312238187469</v>
@@ -2436,7 +2450,7 @@
         <v>0.1373616065961974</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>0.1096970514366013</v>
+        <v>0.1088188087559476</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>0.004383351774619117</v>
@@ -2515,7 +2529,7 @@
         <v>0.1376383919458444</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>0.1125636888620972</v>
+        <v>0.1114829516962353</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>0.002507543882017935</v>
@@ -2594,7 +2608,7 @@
         <v>0.1357137073327654</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>0.1092728999970624</v>
+        <v>0.1083001397465689</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>0.005190476190476191</v>
@@ -2673,7 +2687,7 @@
         <v>0.12878961793308</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>0.1016137507430948</v>
+        <v>0.100648943156759</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>0.003909465020576132</v>
@@ -2752,7 +2766,7 @@
         <v>0.1317536944426887</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>0.1026573866669246</v>
+        <v>0.101569495672799</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>0.004160887656033287</v>
@@ -2831,7 +2845,7 @@
         <v>0.1324486410354609</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>0.1100028002691536</v>
+        <v>0.1093379421534574</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>0.004345613279567787</v>
@@ -2910,7 +2924,7 @@
         <v>0.1390621054961291</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>0.1176615246906213</v>
+        <v>0.1173434615179642</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>0.005360287924037062</v>
@@ -2989,7 +3003,7 @@
         <v>0.1407662015523402</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>0.1200123172383851</v>
+        <v>0.1196898229738855</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>0.005523166615526235</v>
@@ -3068,7 +3082,7 @@
         <v>0.1447913363380809</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>0.1241003426217492</v>
+        <v>0.1237794516577133</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>0.004507512520868113</v>
@@ -3147,7 +3161,7 @@
         <v>0.1451570905231576</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>0.1239101505250861</v>
+        <v>0.1240245622759706</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>0.004748417194268577</v>
@@ -3224,7 +3238,7 @@
         <v>0.152824511992362</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>0.1295356988638232</v>
+        <v>0.1305863598053104</v>
       </c>
       <c r="F34" s="9" t="n">
         <v>0.00569764497341099</v>
@@ -3299,7 +3313,7 @@
         <v>0.1540458324268429</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>0.1308774237742287</v>
+        <v>0.1318263570754138</v>
       </c>
       <c r="F35" s="9" t="n">
         <v>0.006784771956275914</v>
@@ -3372,7 +3386,7 @@
         <v>0.1583426885091907</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>0.1347835616638497</v>
+        <v>0.1362220245321215</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>0.006692261632207389</v>
@@ -3443,7 +3457,7 @@
         <v>0.1590558927494345</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>0.1352301628964691</v>
+        <v>0.1368485535724104</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>0.007178548807094095</v>
@@ -3512,7 +3526,7 @@
         <v>0.1548417411904113</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>0.1314168303094327</v>
+        <v>0.1324128596333872</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>0.007344672476806298</v>
@@ -3579,7 +3593,7 @@
         <v>0.1489021097958185</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>0.125630544450468</v>
+        <v>0.1262286285572796</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>0.006071346526205244</v>
@@ -3644,7 +3658,7 @@
         <v>0.1521364582846645</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>0.137847200718415</v>
+        <v>0.138363610456143</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>0.009204171624553789</v>
@@ -3707,7 +3721,7 @@
         <v>0.150458515523858</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>0.1463624976553851</v>
+        <v>0.1466626469836667</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>0.007134894091415831</v>
@@ -3768,7 +3782,7 @@
         <v>0.1462031928228654</v>
       </c>
       <c r="E42" s="9" t="n">
-        <v>0.1461421164030892</v>
+        <v>0.1462920637695218</v>
       </c>
       <c r="F42" s="9" t="n"/>
       <c r="G42" s="9" t="n"/>
@@ -3819,7 +3833,7 @@
         <v>0.1456686615698962</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>0.1444854781731232</v>
+        <v>0.144518745947101</v>
       </c>
       <c r="F43" s="9" t="n"/>
       <c r="G43" s="9" t="n"/>
@@ -4046,7 +4060,7 @@
         <v>0.1647831307910926</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>0.1373669889219673</v>
+        <v>0.1358394129528923</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>0.002662609357170026</v>
@@ -4125,7 +4139,7 @@
         <v>0.168761002563152</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.1412617208524465</v>
+        <v>0.1398636726498544</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>0.001231375446373599</v>
@@ -4204,7 +4218,7 @@
         <v>0.1601054643738731</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.1324441083184697</v>
+        <v>0.1310458389197806</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0.001351873310158362</v>
@@ -4283,7 +4297,7 @@
         <v>0.1574975375662802</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.1294985300188974</v>
+        <v>0.1281975853169891</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>0.0006750675067506751</v>
@@ -4362,7 +4376,7 @@
         <v>0.1244707638203963</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.1245194488554572</v>
+        <v>0.1237079702720396</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>0</v>
@@ -4441,7 +4455,7 @@
         <v>0.1313883459050301</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.1333670943314159</v>
+        <v>0.1321812940917224</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>0.001443522194153735</v>
@@ -4520,7 +4534,7 @@
         <v>0.1176973107058144</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>0.1220379665928493</v>
+        <v>0.1209246446737693</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>0.0008644910309055544</v>
@@ -4599,7 +4613,7 @@
         <v>0.122354198654347</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0.1139868970238182</v>
+        <v>0.1128741749359049</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>0.0009940357852882703</v>
@@ -4678,7 +4692,7 @@
         <v>0.1227728550520388</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>0.1088541360499014</v>
+        <v>0.1076346203964566</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>0.001774937877174299</v>
@@ -4757,7 +4771,7 @@
         <v>0.12630418701634</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>0.1100234568461662</v>
+        <v>0.1088034780041539</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>0.0009502090459901178</v>
@@ -4836,7 +4850,7 @@
         <v>0.1164418900467493</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>0.1036345643905725</v>
+        <v>0.102442549138361</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>0.001231337540403263</v>
@@ -4915,7 +4929,7 @@
         <v>0.1181190409820631</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.1053486595904616</v>
+        <v>0.104045703881591</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>0.001134705786999514</v>
@@ -4994,7 +5008,7 @@
         <v>0.1129354456675613</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>0.09802977307074948</v>
+        <v>0.09658855283424966</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>0.002040816326530612</v>
@@ -5073,7 +5087,7 @@
         <v>0.1183286460044823</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0.09952867379768809</v>
+        <v>0.09822472212819261</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>0.0009473060982830077</v>
@@ -5152,7 +5166,7 @@
         <v>0.1194296178288019</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>0.09762100314765734</v>
+        <v>0.09630346266618714</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>0.001078894133513149</v>
@@ -5231,7 +5245,7 @@
         <v>0.1200416598918784</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>0.100107189345716</v>
+        <v>0.09843435339365381</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>0.0006590220113351786</v>
@@ -5310,7 +5324,7 @@
         <v>0.1210744478358421</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>0.1001393449049989</v>
+        <v>0.09879237774824336</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>0.001443174984966927</v>
@@ -5389,7 +5403,7 @@
         <v>0.1244794090125384</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.1028704620580924</v>
+        <v>0.1017213595106226</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>0.0009539384028345599</v>
@@ -5468,7 +5482,7 @@
         <v>0.1234626842908238</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>0.1005489556111525</v>
+        <v>0.09936809751794384</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>0.0006532532009406846</v>
@@ -5547,7 +5561,7 @@
         <v>0.129862556413161</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>0.1020140199282135</v>
+        <v>0.1007122175076962</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>0.001221830029866956</v>
@@ -5626,7 +5640,7 @@
         <v>0.1227789046990485</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>0.09719892067383396</v>
+        <v>0.09601078422992051</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>0.0009946007388462632</v>
@@ -5705,7 +5719,7 @@
         <v>0.1226780994355779</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>0.09603972879741432</v>
+        <v>0.09483760110163331</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>0.0009637006103437199</v>
@@ -5784,7 +5798,7 @@
         <v>0.1176441061625953</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>0.09024622913158308</v>
+        <v>0.0888431666720744</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>0.001097333479644464</v>
@@ -5863,7 +5877,7 @@
         <v>0.1228493377117131</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>0.09348417098818752</v>
+        <v>0.09215959641415512</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>0.0008061265618702137</v>
@@ -5942,7 +5956,7 @@
         <v>0.1080252523173347</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>0.08485189275035973</v>
+        <v>0.08366964785963384</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>0.000912512832211703</v>
@@ -6021,7 +6035,7 @@
         <v>0.1163473425221604</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>0.09447086333582373</v>
+        <v>0.09321814272898071</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>0.001081081081081081</v>
@@ -6100,7 +6114,7 @@
         <v>0.1195117928897177</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>0.0985077530337464</v>
+        <v>0.09706247940403194</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>0.000605052185751021</v>
@@ -6179,7 +6193,7 @@
         <v>0.1173759719083341</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>0.09613077993261111</v>
+        <v>0.09459688593079311</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>0.0006838775859121217</v>
@@ -6258,7 +6272,7 @@
         <v>0.1138194687279466</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>0.09227325951244651</v>
+        <v>0.09079712293049866</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>0.0006890611541774332</v>
@@ -6335,7 +6349,7 @@
         <v>0.1142219777757838</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>0.09163990875367178</v>
+        <v>0.09012107314780494</v>
       </c>
       <c r="F34" s="9" t="n">
         <v>0.0005579319323042589</v>
@@ -6410,7 +6424,7 @@
         <v>0.1247723815160504</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>0.1025825990333135</v>
+        <v>0.1009405062537471</v>
       </c>
       <c r="F35" s="9" t="n">
         <v>0.0008279287981233614</v>
@@ -6483,7 +6497,7 @@
         <v>0.1256472975073649</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>0.103573903244297</v>
+        <v>0.1017849182684195</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>0.0006829668078131403</v>
@@ -6554,7 +6568,7 @@
         <v>0.1285042018014208</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>0.1065182063986749</v>
+        <v>0.1046235447583473</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>0.0008762047815746651</v>
@@ -6623,7 +6637,7 @@
         <v>0.1277707998629303</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>0.105852660294613</v>
+        <v>0.1037934017058586</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>0.0009258187709755816</v>
@@ -6690,7 +6704,7 @@
         <v>0.1295923693386644</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>0.107663199182563</v>
+        <v>0.1057573485092276</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>0.001578605255826911</v>
@@ -6755,7 +6769,7 @@
         <v>0.1382925912086581</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>0.1243861921574548</v>
+        <v>0.1229556623779938</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>0.00334777471445451</v>
@@ -6818,7 +6832,7 @@
         <v>0.136140821811199</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>0.1320175392834318</v>
+        <v>0.1303223847064506</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>0.001613668723303275</v>
@@ -6879,7 +6893,7 @@
         <v>0.1321783871188548</v>
       </c>
       <c r="E42" s="9" t="n">
-        <v>0.1319102900519636</v>
+        <v>0.1298423755300882</v>
       </c>
       <c r="F42" s="9" t="n"/>
       <c r="G42" s="9" t="n"/>
@@ -6930,7 +6944,7 @@
         <v>0.1291630102006661</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>0.1273775600010298</v>
+        <v>0.1253490293463322</v>
       </c>
       <c r="F43" s="9" t="n"/>
       <c r="G43" s="9" t="n"/>
@@ -7157,7 +7171,7 @@
         <v>0.1760068872662508</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>0.1489400400548293</v>
+        <v>0.1475899190124463</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>0.007390745501285347</v>
@@ -7236,7 +7250,7 @@
         <v>0.1840185172416542</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.1572345460533346</v>
+        <v>0.1555811003802445</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>0.004636233951497861</v>
@@ -7315,7 +7329,7 @@
         <v>0.1846665765755477</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.1574504098101756</v>
+        <v>0.1562246531073865</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0.007893226176808266</v>
@@ -7394,7 +7408,7 @@
         <v>0.1795061581053794</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.1519381511736987</v>
+        <v>0.1513875282772784</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>0.005707537886242866</v>
@@ -7473,7 +7487,7 @@
         <v>0.1441238007611992</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.1472676538310238</v>
+        <v>0.1472092407870039</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>0.004731488052992667</v>
@@ -7552,7 +7566,7 @@
         <v>0.137055326255005</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.1397446466317124</v>
+        <v>0.1388772576201529</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>0.005456132693147098</v>
@@ -7631,7 +7645,7 @@
         <v>0.1287980958535307</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>0.1357743151873053</v>
+        <v>0.1348273495928165</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>0.003369272237196766</v>
@@ -7710,7 +7724,7 @@
         <v>0.135658197774737</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0.1291863460656681</v>
+        <v>0.128279144096289</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>0.004248432126239126</v>
@@ -7789,7 +7803,7 @@
         <v>0.1377022733786597</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>0.1248550277087181</v>
+        <v>0.1239659980452269</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>0.004113533525298231</v>
@@ -7868,7 +7882,7 @@
         <v>0.1402034707652893</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>0.1244697811912024</v>
+        <v>0.1236025810264263</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>0.003487894952810833</v>
@@ -7947,7 +7961,7 @@
         <v>0.1323755219088188</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>0.1213021319024543</v>
+        <v>0.1201887635236014</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>0.004245283018867924</v>
@@ -8026,7 +8040,7 @@
         <v>0.1322124503128397</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.1206034166485985</v>
+        <v>0.1198290071587663</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>0.00495458298926507</v>
@@ -8105,7 +8119,7 @@
         <v>0.1155471582198858</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>0.1002657850663244</v>
+        <v>0.09979267698276313</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>0.005007363770250369</v>
@@ -8184,7 +8198,7 @@
         <v>0.1339972401767495</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0.1160590717981041</v>
+        <v>0.1153032213445806</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>0.001986316486426837</v>
@@ -8263,7 +8277,7 @@
         <v>0.1291135111651291</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>0.1072182595752308</v>
+        <v>0.1067934372009991</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>0.004396112910689496</v>
@@ -8342,7 +8356,7 @@
         <v>0.1283053076959474</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>0.1078385687326952</v>
+        <v>0.1072190501605765</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>0.003680078508341512</v>
@@ -8421,7 +8435,7 @@
         <v>0.1277131465878496</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>0.1065972231418599</v>
+        <v>0.1057372146275087</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>0.002748625687156422</v>
@@ -8500,7 +8514,7 @@
         <v>0.1284062321397528</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.1066337302093244</v>
+        <v>0.1059417818987717</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>0.00267639902676399</v>
@@ -8579,7 +8593,7 @@
         <v>0.1460842223831064</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>0.1235688567616367</v>
+        <v>0.12325856508603</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>0.0019228128004395</v>
@@ -8658,7 +8672,7 @@
         <v>0.156086815290265</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>0.1279148335254572</v>
+        <v>0.1274965148996195</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>0.00363460140537921</v>
@@ -8737,7 +8751,7 @@
         <v>0.156549002391863</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>0.130878441454396</v>
+        <v>0.1309622260888014</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>0.003041459900752361</v>
@@ -8816,7 +8830,7 @@
         <v>0.1572351762573019</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>0.1299923150718737</v>
+        <v>0.1300985053696513</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>0.005274261603375527</v>
@@ -8895,7 +8909,7 @@
         <v>0.1527630555308201</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>0.1248963657312818</v>
+        <v>0.1247880157671762</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>0.004680415386865584</v>
@@ -8974,7 +8988,7 @@
         <v>0.1522651514493234</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>0.1225280343715954</v>
+        <v>0.1220272934157805</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>0.00421274354923644</v>
@@ -9053,7 +9067,7 @@
         <v>0.1651060511172867</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>0.1429147865320539</v>
+        <v>0.1435036749466387</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>0.005279831045406547</v>
@@ -9132,7 +9146,7 @@
         <v>0.1679493639012578</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>0.1466982410510512</v>
+        <v>0.1477035300052429</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>0.008671047827674333</v>
@@ -9211,7 +9225,7 @@
         <v>0.1720280487376216</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>0.1509857624476127</v>
+        <v>0.1526004916187438</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>0.007797731568998109</v>
@@ -9290,7 +9304,7 @@
         <v>0.1764780845798306</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>0.156002078005273</v>
+        <v>0.1572788747009781</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>0.005962436649110604</v>
@@ -9369,7 +9383,7 @@
         <v>0.1810039592733451</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>0.1595296839053354</v>
+        <v>0.1618231392008733</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>0.005512220488819553</v>
@@ -9446,7 +9460,7 @@
         <v>0.1958707602630508</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>0.171341001289553</v>
+        <v>0.1754676771288392</v>
       </c>
       <c r="F34" s="9" t="n">
         <v>0.007606787595084845</v>
@@ -9521,7 +9535,7 @@
         <v>0.1927477924523951</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>0.1683902957545456</v>
+        <v>0.1722315344843431</v>
       </c>
       <c r="F35" s="9" t="n">
         <v>0.01019184652278178</v>
@@ -9594,7 +9608,7 @@
         <v>0.1974858082552343</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>0.1725084240743978</v>
+        <v>0.177126093992667</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>0.01098901098901099</v>
@@ -9665,7 +9679,7 @@
         <v>0.1999500578971476</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>0.1741846163880079</v>
+        <v>0.1795834168636766</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>0.01252333540759179</v>
@@ -9734,7 +9748,7 @@
         <v>0.1967993320876152</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>0.1714630282086148</v>
+        <v>0.1763527003911408</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>0.01274800251369064</v>
@@ -9801,7 +9815,7 @@
         <v>0.1881928463842645</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>0.1633105650250532</v>
+        <v>0.1673016660613234</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>0.01005896635449185</v>
@@ -9866,7 +9880,7 @@
         <v>0.1887110782136452</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>0.1747808672123263</v>
+        <v>0.1783824245788371</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>0.01597228904070047</v>
@@ -9929,7 +9943,7 @@
         <v>0.1866387202038333</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>0.1845214306887481</v>
+        <v>0.1879448204320203</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>0.01296551724137931</v>
@@ -9990,7 +10004,7 @@
         <v>0.1792801283472147</v>
       </c>
       <c r="E42" s="9" t="n">
-        <v>0.1819416546047714</v>
+        <v>0.1851156421215646</v>
       </c>
       <c r="F42" s="9" t="n"/>
       <c r="G42" s="9" t="n"/>
@@ -10041,7 +10055,7 @@
         <v>0.1812530223447609</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>0.1827914426277447</v>
+        <v>0.1859482666691393</v>
       </c>
       <c r="F43" s="9" t="n"/>
       <c r="G43" s="9" t="n"/>
@@ -10268,7 +10282,7 @@
         <v>0.2007129903743641</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>0.1733997282158314</v>
+        <v>0.1736127821020439</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>0.01050175029171529</v>
@@ -10347,7 +10361,7 @@
         <v>0.1950328371673822</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.1681642746718575</v>
+        <v>0.167726191661055</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>0.01806451612903226</v>
@@ -10426,7 +10440,7 @@
         <v>0.1917378086040138</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.1640280505679344</v>
+        <v>0.1637568253580393</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0.01183431952662722</v>
@@ -10505,7 +10519,7 @@
         <v>0.1604963214547955</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.1324701582811089</v>
+        <v>0.1311315402447217</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>0.007614213197969543</v>
@@ -10584,7 +10598,7 @@
         <v>0.1248604846906471</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.1265852559304815</v>
+        <v>0.1249818664243621</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>0.005830903790087463</v>
@@ -10663,7 +10677,7 @@
         <v>0.1268258089966634</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.1282270275183014</v>
+        <v>0.1267662613191632</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>0.01176470588235294</v>
@@ -10742,7 +10756,7 @@
         <v>0.1134870259165308</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>0.1186815432326419</v>
+        <v>0.1167485940472008</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>0.01223241590214067</v>
@@ -10821,7 +10835,7 @@
         <v>0.1255146142084466</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0.1180927332736926</v>
+        <v>0.1173166929567017</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>0.005830903790087463</v>
@@ -10900,7 +10914,7 @@
         <v>0.1253457211311264</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>0.1127592709970741</v>
+        <v>0.1110283762692514</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>0</v>
@@ -10979,7 +10993,7 @@
         <v>0.1324658064721999</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>0.11784627049073</v>
+        <v>0.1162578726381399</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>0.005681818181818182</v>
@@ -11058,7 +11072,7 @@
         <v>0.1112614252254807</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>0.09873436799122441</v>
+        <v>0.09744055556354669</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>0</v>
@@ -11137,7 +11151,7 @@
         <v>0.1331173022303523</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.1221147304274158</v>
+        <v>0.1206304259122283</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>0</v>
@@ -11216,7 +11230,7 @@
         <v>0.1118519710914956</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>0.09735000694627667</v>
+        <v>0.09537023226264356</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>0</v>
@@ -11295,7 +11309,7 @@
         <v>0.1253252647804549</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0.1062978340231439</v>
+        <v>0.1055664121910538</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>0</v>
@@ -11374,7 +11388,7 @@
         <v>0.1198927255369458</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>0.09732258506199896</v>
+        <v>0.09634364340078612</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>0.007905138339920948</v>
@@ -11453,7 +11467,7 @@
         <v>0.1249429710227454</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>0.1034472383487359</v>
+        <v>0.1030421841404095</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>0</v>
@@ -11532,7 +11546,7 @@
         <v>0.1155406861437549</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>0.09449023627832095</v>
+        <v>0.09299246547549113</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>0</v>
@@ -11611,7 +11625,7 @@
         <v>0.1250812496612037</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.104021200951397</v>
+        <v>0.1028290119247325</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>0</v>
@@ -11690,7 +11704,7 @@
         <v>0.1129507094449481</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>0.08962305380567308</v>
+        <v>0.0889606579346703</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>0.004201680672268907</v>
@@ -11769,7 +11783,7 @@
         <v>0.1508943020577949</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>0.1231120343309703</v>
+        <v>0.1220486696296397</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>0.005415162454873646</v>
@@ -11848,7 +11862,7 @@
         <v>0.1507212935992684</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>0.1250493673580865</v>
+        <v>0.1243062045080212</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>0.001639344262295082</v>
@@ -11927,7 +11941,7 @@
         <v>0.145720982291879</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>0.1191692620382979</v>
+        <v>0.1182340998534005</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>0.007692307692307693</v>
@@ -12006,7 +12020,7 @@
         <v>0.1334630320175305</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>0.1060942630613313</v>
+        <v>0.105582158048375</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>0.00535475234270415</v>
@@ -12085,7 +12099,7 @@
         <v>0.1388121667866674</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>0.1100283553644338</v>
+        <v>0.108796379493882</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>0.003210272873194221</v>
@@ -12164,7 +12178,7 @@
         <v>0.1393151821844556</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>0.1170270293588806</v>
+        <v>0.1162011730603047</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>0.008888888888888889</v>
@@ -12243,7 +12257,7 @@
         <v>0.1455616525346343</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>0.1243765407191287</v>
+        <v>0.1241842120709632</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>0.005639097744360902</v>
@@ -12322,7 +12336,7 @@
         <v>0.1332402163723539</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>0.1129755982722836</v>
+        <v>0.1117658312062143</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>0.002109704641350211</v>
@@ -12401,7 +12415,7 @@
         <v>0.1319383195565887</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>0.1113550443701961</v>
+        <v>0.1104347134438877</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>0.00423728813559322</v>
@@ -12480,7 +12494,7 @@
         <v>0.1354317862209026</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>0.1148164135877099</v>
+        <v>0.1140180347120785</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>0.003868471953578337</v>
@@ -12557,7 +12571,7 @@
         <v>0.1432548675197855</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>0.1214634018060547</v>
+        <v>0.1210670550059376</v>
       </c>
       <c r="F34" s="9" t="n">
         <v>0.003883495145631068</v>
@@ -12632,7 +12646,7 @@
         <v>0.1460980776946432</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>0.1240884913721496</v>
+        <v>0.1242813320355281</v>
       </c>
       <c r="F35" s="9" t="n">
         <v>0</v>
@@ -12705,7 +12719,7 @@
         <v>0.1373164778536496</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>0.1154935672974057</v>
+        <v>0.1149950280816063</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>0</v>
@@ -12776,7 +12790,7 @@
         <v>0.1345292527621496</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>0.1113396823479756</v>
+        <v>0.1118388687689553</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>0.002604166666666667</v>
@@ -12845,7 +12859,7 @@
         <v>0.1427772083826232</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>0.1200724664540001</v>
+        <v>0.1201829011472376</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>0.001754385964912281</v>
@@ -12912,7 +12926,7 @@
         <v>0.1477371734413175</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>0.125288798442514</v>
+        <v>0.125417004548698</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>0.003629764065335753</v>
@@ -12977,7 +12991,7 @@
         <v>0.1444977810946259</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>0.1304919825808435</v>
+        <v>0.1301520337193116</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>0</v>
@@ -13040,7 +13054,7 @@
         <v>0.1439676392249817</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>0.1398406445998991</v>
+        <v>0.1393779682699878</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>0.007971014492753623</v>
@@ -13101,7 +13115,7 @@
         <v>0.1450648113286439</v>
       </c>
       <c r="E42" s="9" t="n">
-        <v>0.1446525698356121</v>
+        <v>0.1449281231006304</v>
       </c>
       <c r="F42" s="9" t="n"/>
       <c r="G42" s="9" t="n"/>
@@ -13152,7 +13166,7 @@
         <v>0.1394301871223121</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>0.1382274931781584</v>
+        <v>0.137505782185995</v>
       </c>
       <c r="F43" s="9" t="n"/>
       <c r="G43" s="9" t="n"/>
@@ -13379,7 +13393,7 @@
         <v>0.1628693777314506</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>0.1361148000258901</v>
+        <v>0.1339763257067486</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>0.00670621614650503</v>
@@ -13458,7 +13472,7 @@
         <v>0.1494665158895451</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.1222995100325702</v>
+        <v>0.1204308212630295</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>0.001223241590214067</v>
@@ -13537,7 +13551,7 @@
         <v>0.1533249359558859</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.1262820287974614</v>
+        <v>0.1243510207837713</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0.002705139765554554</v>
@@ -13616,7 +13630,7 @@
         <v>0.1592472937279113</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.1324638384446907</v>
+        <v>0.1305084881151846</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>0.00749375520399667</v>
@@ -13695,7 +13709,7 @@
         <v>0.1294787542790824</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.1316687434204068</v>
+        <v>0.1295594844219896</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>0.004016064257028112</v>
@@ -13774,7 +13788,7 @@
         <v>0.133311817776777</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.1366542840946088</v>
+        <v>0.1343879396729252</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>0.005882352941176471</v>
@@ -13853,7 +13867,7 @@
         <v>0.1233243359197484</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>0.1304071162657094</v>
+        <v>0.1281700874969506</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>0.00396039603960396</v>
@@ -13932,7 +13946,7 @@
         <v>0.1267958915928095</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0.1202115846004541</v>
+        <v>0.1179493095925534</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>0.002649006622516556</v>
@@ -14011,7 +14025,7 @@
         <v>0.1277298057352472</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>0.1150982447048232</v>
+        <v>0.1128041705791211</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>0.003101736972704715</v>
@@ -14090,7 +14104,7 @@
         <v>0.1363159760616384</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>0.1215752038540228</v>
+        <v>0.1191440936874586</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>0.009124087591240875</v>
@@ -14169,7 +14183,7 @@
         <v>0.134978393757888</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>0.1251509620166895</v>
+        <v>0.1229881236818814</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>0.01058574453069866</v>
@@ -14248,7 +14262,7 @@
         <v>0.1285060639208936</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.1183642346213995</v>
+        <v>0.1159007711429499</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>0.01483171705647461</v>
@@ -14327,7 +14341,7 @@
         <v>0.1355957553755318</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>0.1236424088442422</v>
+        <v>0.1215761570048713</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>0.01377410468319559</v>
@@ -14406,7 +14420,7 @@
         <v>0.1365236835393159</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0.119267642082082</v>
+        <v>0.1171732903505085</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>0.006000705965407695</v>
@@ -14485,7 +14499,7 @@
         <v>0.1367166246482283</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>0.1160382334078098</v>
+        <v>0.1139823188666638</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>0.006056287851799074</v>
@@ -14564,7 +14578,7 @@
         <v>0.1371088256330188</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>0.1185396544590235</v>
+        <v>0.1163400586953284</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>0.007676902536715621</v>
@@ -14643,7 +14657,7 @@
         <v>0.1467351696555365</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>0.1274974809265594</v>
+        <v>0.1257605032206868</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>0.005702950657079098</v>
@@ -14722,7 +14736,7 @@
         <v>0.1469596996971839</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.1272459998361255</v>
+        <v>0.1252860371943297</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>0.007640317367029092</v>
@@ -14801,7 +14815,7 @@
         <v>0.1416035166912635</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>0.1199567769939841</v>
+        <v>0.1180707909146485</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>0.007859949982136478</v>
@@ -14880,7 +14894,7 @@
         <v>0.1472390637211843</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>0.1198722607927275</v>
+        <v>0.117932881001882</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>0.008846657929226736</v>
@@ -14959,7 +14973,7 @@
         <v>0.1538517398523786</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>0.1295322845540462</v>
+        <v>0.1271090875621042</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>0.00337193959829937</v>
@@ -15038,7 +15052,7 @@
         <v>0.1483420271596743</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>0.1224517769206011</v>
+        <v>0.1200706709364847</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>0.01017728168089297</v>
@@ -15117,7 +15131,7 @@
         <v>0.1454304518319132</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>0.1187520390669976</v>
+        <v>0.1164342793513876</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>0.008088070096607504</v>
@@ -15196,7 +15210,7 @@
         <v>0.14823869999618</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>0.1191454988467709</v>
+        <v>0.1170420609748146</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>0.009675967596759675</v>
@@ -15275,7 +15289,7 @@
         <v>0.1424779711483818</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>0.1213514613726197</v>
+        <v>0.1190676525163786</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>0.009222919937205651</v>
@@ -15354,7 +15368,7 @@
         <v>0.1370534886507126</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>0.1169355289553168</v>
+        <v>0.1146923905608326</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>0.006622516556291391</v>
@@ -15433,7 +15447,7 @@
         <v>0.141226058658709</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>0.1219619053497051</v>
+        <v>0.1195892233444783</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>0.009948269001193792</v>
@@ -15512,7 +15526,7 @@
         <v>0.1414175864677958</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>0.1217824743101112</v>
+        <v>0.119526929250212</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>0.006958811359789355</v>
@@ -15591,7 +15605,7 @@
         <v>0.1446781351789757</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>0.1252197008704602</v>
+        <v>0.1231068542942323</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>0.008435428800964049</v>
@@ -15668,7 +15682,7 @@
         <v>0.1437041214350047</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>0.1224097764548303</v>
+        <v>0.1204607183077246</v>
       </c>
       <c r="F34" s="9" t="n">
         <v>0.007791629563668744</v>
@@ -15743,7 +15757,7 @@
         <v>0.1419560941322973</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>0.1205677715951929</v>
+        <v>0.1185520657831605</v>
       </c>
       <c r="F35" s="9" t="n">
         <v>0.009426751592356689</v>
@@ -15816,7 +15830,7 @@
         <v>0.1397950623310689</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>0.1184358884034746</v>
+        <v>0.1162028234761349</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>0.005648197955890263</v>
@@ -15887,7 +15901,7 @@
         <v>0.1405844445805216</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>0.1193413703086288</v>
+        <v>0.1171527356709832</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>0.005511622334052241</v>
@@ -15956,7 +15970,7 @@
         <v>0.1464657426648131</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>0.125002892478353</v>
+        <v>0.1231724004780741</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>0.008089607965152458</v>
@@ -16023,7 +16037,7 @@
         <v>0.141885627445472</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>0.1201715100414514</v>
+        <v>0.1183773037538525</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>0.005937921727395412</v>
@@ -16088,7 +16102,7 @@
         <v>0.1463857051387521</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>0.133562961580541</v>
+        <v>0.1317730448755334</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>0.00823045267489712</v>
@@ -16151,7 +16165,7 @@
         <v>0.1489306789673813</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>0.1465012112071653</v>
+        <v>0.1449081079485941</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>0.006918819188191882</v>
@@ -16212,7 +16226,7 @@
         <v>0.1384608891487341</v>
       </c>
       <c r="E42" s="9" t="n">
-        <v>0.1390055517155848</v>
+        <v>0.1370755575833351</v>
       </c>
       <c r="F42" s="9" t="n"/>
       <c r="G42" s="9" t="n"/>
@@ -16263,7 +16277,7 @@
         <v>0.1373976157006845</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>0.1368650990490194</v>
+        <v>0.1345656123348273</v>
       </c>
       <c r="F43" s="9" t="n"/>
       <c r="G43" s="9" t="n"/>
@@ -30710,7 +30724,7 @@
         <v>0.1697302748267528</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>0.1425702784669757</v>
+        <v>0.1410547877378319</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>0.005412576280180419</v>
@@ -30789,7 +30803,7 @@
         <v>0.1729214610076629</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.1457911433142464</v>
+        <v>0.1442500576370642</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>0.003255904363883759</v>
@@ -30868,7 +30882,7 @@
         <v>0.1706303560993175</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.143286477207469</v>
+        <v>0.141900067921762</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0.004891943773608273</v>
@@ -30947,7 +30961,7 @@
         <v>0.1670105832696708</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.139425419675712</v>
+        <v>0.1383051144902723</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>0.004301598896193491</v>
@@ -31026,7 +31040,7 @@
         <v>0.1330364946297469</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.1347054597270831</v>
+        <v>0.1339545002273516</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>0.002701947265443026</v>
@@ -31105,7 +31119,7 @@
         <v>0.133669299163202</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.1360770928524418</v>
+        <v>0.1348673005519391</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>0.00383525095881274</v>
@@ -31184,7 +31198,7 @@
         <v>0.1228771363216597</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>0.1286981566173996</v>
+        <v>0.1274722245310928</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>0.00265543448402161</v>
@@ -31263,7 +31277,7 @@
         <v>0.1285737696440496</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0.1212538052504621</v>
+        <v>0.1200899706041318</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>0.002705902249281245</v>
@@ -31342,7 +31356,7 @@
         <v>0.1293322652446746</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>0.1160322557088448</v>
+        <v>0.1147906667124662</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>0.00282303597354412</v>
@@ -31421,7 +31435,7 @@
         <v>0.13342365455931</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>0.1176195735080117</v>
+        <v>0.1163665135485878</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>0.003214638971315529</v>
@@ -31500,7 +31514,7 @@
         <v>0.1251508938534342</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>0.1133990960055632</v>
+        <v>0.1121450872226465</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>0.003445661911653229</v>
@@ -31579,7 +31593,7 @@
         <v>0.125680453106082</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.113761732525428</v>
+        <v>0.1125368524408116</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>0.004416403785488959</v>
@@ -31658,7 +31672,7 @@
         <v>0.1173323917087008</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>0.1027955925383465</v>
+        <v>0.1015338803574728</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>0.004772425983208131</v>
@@ -31737,7 +31751,7 @@
         <v>0.1260661151562001</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0.1077760132522865</v>
+        <v>0.1064977500066081</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>0.002111145606954362</v>
@@ -31816,7 +31830,7 @@
         <v>0.1255454238294707</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>0.1039128871676985</v>
+        <v>0.1027218167257971</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>0.00310873825775495</v>
@@ -31895,7 +31909,7 @@
         <v>0.1258153246818414</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>0.1059884418149672</v>
+        <v>0.1045158286872714</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>0.002892700975445678</v>
@@ -31974,7 +31988,7 @@
         <v>0.1288403343870299</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>0.1082728148167998</v>
+        <v>0.1069464066695982</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>0.002774092389337836</v>
@@ -32053,7 +32067,7 @@
         <v>0.1306398721063738</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.1094221415713826</v>
+        <v>0.1082139759419328</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>0.002922034798778058</v>
@@ -32132,7 +32146,7 @@
         <v>0.1353134387269145</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>0.1127529411273731</v>
+        <v>0.1118218234560582</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>0.002336968617849989</v>
@@ -32211,7 +32225,7 @@
         <v>0.1444854483388257</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>0.1165764336663428</v>
+        <v>0.1155595830612563</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>0.003588890044731093</v>
@@ -32290,7 +32304,7 @@
         <v>0.1440163282410938</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>0.1188213677592024</v>
+        <v>0.1176232282679054</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>0.002413593357791079</v>
@@ -32369,7 +32383,7 @@
         <v>0.1423740726484915</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>0.1157985469546441</v>
+        <v>0.1146179133256061</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>0.005505775666630681</v>
@@ -32448,7 +32462,7 @@
         <v>0.135404746365845</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>0.1080077586048284</v>
+        <v>0.1068622229590486</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>0.003877435218460375</v>
@@ -32527,7 +32541,7 @@
         <v>0.1387968886190033</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>0.1094016124977839</v>
+        <v>0.1081478788431385</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>0.004119294776734223</v>
@@ -32606,7 +32620,7 @@
         <v>0.1376506547714917</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>0.1153184840781932</v>
+        <v>0.1145578324181424</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>0.004596504921729327</v>
@@ -32685,7 +32699,7 @@
         <v>0.1441963469977625</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>0.1229221572808477</v>
+        <v>0.1225595558850763</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>0.005609041439933026</v>
@@ -32764,7 +32778,7 @@
         <v>0.1467361312606717</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>0.126158406732995</v>
+        <v>0.1257508166669354</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>0.005880923450789793</v>
@@ -32843,7 +32857,7 @@
         <v>0.1509895036587559</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>0.1305098769477212</v>
+        <v>0.1301158642225724</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>0.004746325054144971</v>
@@ -32922,7 +32936,7 @@
         <v>0.1525839430537038</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>0.1315907993248431</v>
+        <v>0.131712714357672</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>0.004828839166188563</v>
@@ -32999,7 +33013,7 @@
         <v>0.1619306871061364</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>0.1386809179356907</v>
+        <v>0.1399014270550064</v>
       </c>
       <c r="F34" s="9" t="n">
         <v>0.005717608295377459</v>
@@ -33074,7 +33088,7 @@
         <v>0.1620798449778373</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>0.1389468243235369</v>
+        <v>0.1400216171219286</v>
       </c>
       <c r="F35" s="9" t="n">
         <v>0.006924852526288792</v>
@@ -33147,7 +33161,7 @@
         <v>0.1671436943860002</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>0.1435939025506326</v>
+        <v>0.1452574007575879</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>0.007033857892226991</v>
@@ -33218,7 +33232,7 @@
         <v>0.1667386872219692</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>0.142943758582898</v>
+        <v>0.1447282260387432</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>0.007558459963782379</v>
@@ -33287,7 +33301,7 @@
         <v>0.162238671324329</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>0.1388772698477784</v>
+        <v>0.1399860915401042</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>0.007548369154979937</v>
@@ -33354,7 +33368,7 @@
         <v>0.1571303069685226</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>0.1339380201269472</v>
+        <v>0.1346506148672444</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>0.005911812328199722</v>
@@ -33419,7 +33433,7 @@
         <v>0.1606724742328915</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>0.1469003101999537</v>
+        <v>0.1475621816444056</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>0.009152950622240065</v>
@@ -33482,7 +33496,7 @@
         <v>0.1588283715302923</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>0.1557798671545093</v>
+        <v>0.1562157854957739</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>0.007336135073361351</v>
@@ -33543,7 +33557,7 @@
         <v>0.1539917064107829</v>
       </c>
       <c r="E42" s="9" t="n">
-        <v>0.1550994814253076</v>
+        <v>0.1554181398511428</v>
       </c>
       <c r="F42" s="9" t="n"/>
       <c r="G42" s="9" t="n"/>
@@ -33594,7 +33608,7 @@
         <v>0.1540411035862974</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>0.1539578539081442</v>
+        <v>0.1542409713933532</v>
       </c>
       <c r="F43" s="9" t="n"/>
       <c r="G43" s="9" t="n"/>
@@ -33821,7 +33835,7 @@
         <v>0.1732909724914043</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>0.1463153363827889</v>
+        <v>0.1448085439824769</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>0.007391859828435846</v>
@@ -33900,7 +33914,7 @@
         <v>0.1756337579513791</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.1487439762445087</v>
+        <v>0.1471096412030216</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>0.004575740547483343</v>
@@ -33979,7 +33993,7 @@
         <v>0.1755978056804268</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.1484037669811668</v>
+        <v>0.1470229553315022</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0.006562756357670222</v>
@@ -34058,7 +34072,7 @@
         <v>0.1723775980095297</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.1450259144878084</v>
+        <v>0.1440075214530844</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>0.006347594261774787</v>
@@ -34137,7 +34151,7 @@
         <v>0.1390337273522765</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.1418371194851357</v>
+        <v>0.1411285319717646</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>0.004593695548867417</v>
@@ -34216,7 +34230,7 @@
         <v>0.1356285432668579</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.1384048690154185</v>
+        <v>0.137174468531251</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>0.005889646621202728</v>
@@ -34295,7 +34309,7 @@
         <v>0.1266850570595874</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>0.1335943592299821</v>
+        <v>0.1322856423893444</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>0.003972036860502065</v>
@@ -34374,7 +34388,7 @@
         <v>0.1331771307503185</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0.1266323438584697</v>
+        <v>0.125430678698773</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>0.003972925250147146</v>
@@ -34453,7 +34467,7 @@
         <v>0.1347958543968493</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>0.1220111921604249</v>
+        <v>0.1207512174138851</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>0.003696037847427557</v>
@@ -34532,7 +34546,7 @@
         <v>0.1388767314459342</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>0.1234377344795737</v>
+        <v>0.1221593364066388</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>0.004949053857350801</v>
@@ -34611,7 +34625,7 @@
         <v>0.1322113377930439</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>0.1213152629512327</v>
+        <v>0.1200109956246433</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>0.005240828550037434</v>
@@ -34690,7 +34704,7 @@
         <v>0.1314421071813133</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.1201723361489221</v>
+        <v>0.1190069482241407</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>0.00691699604743083</v>
@@ -34769,7 +34783,7 @@
         <v>0.1220893452913871</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>0.1079516216955627</v>
+        <v>0.1068841151020086</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>0.007727690892364305</v>
@@ -34848,7 +34862,7 @@
         <v>0.134596523378949</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0.116868543499556</v>
+        <v>0.1156186012380989</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>0.003394255874673629</v>
@@ -34927,7 +34941,7 @@
         <v>0.1316885695210122</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>0.1102328980060357</v>
+        <v>0.1091688629669253</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>0.005147656461663506</v>
@@ -35006,7 +35020,7 @@
         <v>0.1318341203346924</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>0.1121193929669607</v>
+        <v>0.1108555034677985</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>0.005221214619400934</v>
@@ -35085,7 +35099,7 @@
         <v>0.1366513113645463</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>0.1164535094238669</v>
+        <v>0.1151477796563002</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>0.004112737389621386</v>
@@ -35164,7 +35178,7 @@
         <v>0.136495503995307</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.1156496317616059</v>
+        <v>0.1143853256016419</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>0.004792746113989638</v>
@@ -35243,7 +35257,7 @@
         <v>0.1441044519517486</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>0.1218059848510747</v>
+        <v>0.1210601272291081</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>0.003585966272533437</v>
@@ -35322,7 +35336,7 @@
         <v>0.1535674232059798</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>0.1256208467856565</v>
+        <v>0.1247809738426664</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>0.00505902192242833</v>
@@ -35401,7 +35415,7 @@
         <v>0.1549440213898667</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>0.1299471743527704</v>
+        <v>0.1287438878043389</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>0.003143734464102939</v>
@@ -35480,7 +35494,7 @@
         <v>0.1523437579512233</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>0.1258000430397589</v>
+        <v>0.1246302892529601</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>0.007804878048780488</v>
@@ -35559,7 +35573,7 @@
         <v>0.1488532477511557</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>0.121456933352621</v>
+        <v>0.1205063991072161</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>0.005982550893228085</v>
@@ -35638,7 +35652,7 @@
         <v>0.1498241667129239</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>0.1204080707991519</v>
+        <v>0.1192033216263904</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>0.00641025641025641</v>
@@ -35717,7 +35731,7 @@
         <v>0.155820929244389</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>0.1340046885115999</v>
+        <v>0.1335026144262889</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>0.006856023506366308</v>
@@ -35796,7 +35810,7 @@
         <v>0.159091493946647</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>0.1381394410644857</v>
+        <v>0.1382529233456929</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>0.008030838419530999</v>
@@ -35875,7 +35889,7 @@
         <v>0.1596249955524489</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>0.1392491022074817</v>
+        <v>0.1393327844157936</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>0.008378688054998567</v>
@@ -35954,7 +35968,7 @@
         <v>0.1633920741361857</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>0.1431949222695341</v>
+        <v>0.1432214978352785</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>0.006245268735806208</v>
@@ -36033,7 +36047,7 @@
         <v>0.1674755963831341</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>0.1466949167631968</v>
+        <v>0.1474307348880632</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>0.006419164846800344</v>
@@ -36110,7 +36124,7 @@
         <v>0.1787401838671158</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>0.1552551598839062</v>
+        <v>0.1574408388208816</v>
       </c>
       <c r="F34" s="9" t="n">
         <v>0.007535548129218268</v>
@@ -36185,7 +36199,7 @@
         <v>0.1788239576741628</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>0.1552675985031523</v>
+        <v>0.1575617676428744</v>
       </c>
       <c r="F35" s="9" t="n">
         <v>0.009661237381556945</v>
@@ -36258,7 +36272,7 @@
         <v>0.1841697057937505</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>0.1600141466195495</v>
+        <v>0.1630942019851395</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>0.009639634590595752</v>
@@ -36329,7 +36343,7 @@
         <v>0.1842804838121468</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>0.1596556253720646</v>
+        <v>0.1631280594246665</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>0.01062424625279963</v>
@@ -36398,7 +36412,7 @@
         <v>0.1802566312334607</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>0.1561407696148021</v>
+        <v>0.1589056942538196</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>0.01101028433151845</v>
@@ -36465,7 +36479,7 @@
         <v>0.1759139432958562</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>0.1518600841470938</v>
+        <v>0.1543587213664516</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>0.008867494299467951</v>
@@ -36530,7 +36544,7 @@
         <v>0.1760777942812929</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>0.1623980316883378</v>
+        <v>0.1645002194422691</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>0.01314897654873255</v>
@@ -36593,7 +36607,7 @@
         <v>0.1732345758754582</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>0.1708685371636589</v>
+        <v>0.1726576502004646</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>0.01096980290518956</v>
@@ -36654,7 +36668,7 @@
         <v>0.1672698734027157</v>
       </c>
       <c r="E42" s="9" t="n">
-        <v>0.169215166954061</v>
+        <v>0.170986576046314</v>
       </c>
       <c r="F42" s="9" t="n"/>
       <c r="G42" s="9" t="n"/>
@@ -36705,7 +36719,7 @@
         <v>0.1676577103942724</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>0.1685061315982114</v>
+        <v>0.1700544908891963</v>
       </c>
       <c r="F43" s="9" t="n"/>
       <c r="G43" s="9" t="n"/>

--- a/entregables/TCNB_calibracion_series.xlsx
+++ b/entregables/TCNB_calibracion_series.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A40"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -604,154 +604,202 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Fuera de IBK el nodo de politica no existe (16_nodo.sql pone SIN_ALCANCE para</t>
+          <t>Fuera de IBK se EXTRAPOLA la calibracion de IBK: los mismos coeficientes, sin</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>entidad &lt;&gt; 00002), asi que la BetaCal por nodo no se puede aplicar. Se usa una</t>
+          <t>reajustar nada. No se puede calibrar distinto por entidad, y produccion tampoco</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>BetaCal GLOBAL ajustada sobre IBK, mas el mismo corrimiento probit, el mismo</t>
+          <t>podria.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>driver y el mismo F del mes. Los coeficientes son UNO SOLO para las cinco</t>
-        </is>
-      </c>
+      <c r="A20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>entidades: no se diferencia por entidad.</t>
+          <t>El nodo se reconstruye replicando el CASE de 16_nodo.sql: sus cinco banderas si</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   BetaCal   a = 1.472959   b = 0.000000   m = 1.094112</t>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>existen para todas las entidades. La replica reproduce el nodo real de IBK en</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ajustada con la restriccion monotona del pipeline (a&gt;=0, b&gt;=0). Sin ella el</t>
+          <t>1,690,263 filas sin una discrepancia, y la cadena reproduce el pd_pit del</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ajuste global da b&lt;0 y la PD calibrada decrece por encima de 58% de PD cruda.</t>
+          <t>pipeline con diferencia maxima 5.1e-09.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">   corrimiento probit = -0.271976     delta_0 = +0.182368</t>
+          <t xml:space="preserve">   nodo    a           b           m           probit_delta</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">   N1      1.825693   0.079454   1.469515   -0.160355</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   N2      1.464358   0.000000   0.902603   -0.266690</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   N3      1.327667   0.000000   0.949176   -0.274082</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   delta_0 = +0.182368     driver {'seg_arq_salud=C': -0.03501742387469351}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">   rho = 0.0332     lambda = 1.0     LRA = 6.9834%</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>PROYECCION DE LA MORA</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Los meses sin mora 12m cerrada se proyectan por chain-ladder: se toma el ultimo</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>horizonte con dato y se multiplica por el factor h-&gt;12 de la propia hoja.</t>
-        </is>
-      </c>
-    </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>V1, V2 y V3 son el P25, la mediana y el P75 de los factores historicos, y solo</t>
-        </is>
-      </c>
+      <c r="A31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>se calculan en las hojas de IBK.</t>
+          <t>OJO: fuera de IBK el nodo reconstruido se va a N3 (88-93%), porque PLIN cubre</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr"/>
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>57% en IBK y 9-18% en el resto. No es que esos clientes sean peores: es que IBK</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>COLUMNAS CALCULADAS</t>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>no los ve. Es la consecuencia honesta de extrapolar.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>EC vigente        PD cal vigente / mora 12m  - 1</t>
-        </is>
-      </c>
+      <c r="A35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>EC NUEVA          PD cal NUEVA   / mora 12m  - 1</t>
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>PROYECCION DE LA MORA</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>EC NUEVA vs proy  PD cal NUEVA   / proy      - 1   (para los meses sin mora cerrada)</t>
+          <t>Los meses sin mora 12m cerrada se proyectan por chain-ladder: se toma el ultimo</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
+          <t>horizonte con dato y se multiplica por el factor h-&gt;12 de la propia hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>V1, V2 y V3 son el P25, la mediana y el P75 de los factores historicos, y solo</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>se calculan en las hojas de IBK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>COLUMNAS CALCULADAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>EC vigente        PD cal vigente / mora 12m  - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>EC NUEVA          PD cal NUEVA   / mora 12m  - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>EC NUEVA vs proy  PD cal NUEVA   / proy      - 1   (para los meses sin mora cerrada)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
           <t>Son formulas vivas: si se edita una celda de entrada, el error se recalcula.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Generado por Programas/reportes/10_excel_series.py</t>
         </is>
@@ -949,7 +997,7 @@
         <v>0.1660379595796832</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>0.1375568991854284</v>
+        <v>0.1476113205422589</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>0.007111597374179431</v>
@@ -1028,7 +1076,7 @@
         <v>0.1664079985963771</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.1378731848332384</v>
+        <v>0.1478658155043509</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>0.00471342383107089</v>
@@ -1107,7 +1155,7 @@
         <v>0.1629954402597873</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.1345153431147133</v>
+        <v>0.1437745887725968</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0.006322668250869897</v>
@@ -1186,7 +1234,7 @@
         <v>0.1578369241884913</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.1294873717460337</v>
+        <v>0.1384925472961645</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>0.006436179301703025</v>
@@ -1265,7 +1313,7 @@
         <v>0.1233364785159737</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.122226938082706</v>
+        <v>0.1313872620388031</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>0.003405704555129843</v>
@@ -1344,7 +1392,7 @@
         <v>0.1244268395551793</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.1234328437425222</v>
+        <v>0.1325466641855836</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>0.00411775551594862</v>
@@ -1423,7 +1471,7 @@
         <v>0.1156866766943294</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>0.118857558833138</v>
+        <v>0.1286113172765142</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>0.003478765038411364</v>
@@ -1502,7 +1550,7 @@
         <v>0.1228169047329705</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0.1137794656282025</v>
+        <v>0.1232605663077515</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>0.003286713286713287</v>
@@ -1581,7 +1629,7 @@
         <v>0.1298233347756259</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>0.1154754444868372</v>
+        <v>0.1249493705861273</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>0.003275681341719077</v>
@@ -1660,7 +1708,7 @@
         <v>0.1356364520438287</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>0.1191038044872064</v>
+        <v>0.1279624424332394</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>0.005481042042816611</v>
@@ -1739,7 +1787,7 @@
         <v>0.1237410325682142</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>0.1111886346644216</v>
+        <v>0.1196912698332674</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>0.004803022126281705</v>
@@ -1818,7 +1866,7 @@
         <v>0.1249736210942026</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.1123403471016208</v>
+        <v>0.120883944641389</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>0.006160277212474561</v>
@@ -1897,7 +1945,7 @@
         <v>0.1167956862047136</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>0.1016809175837778</v>
+        <v>0.1095811496574861</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>0.007068771883464359</v>
@@ -1976,7 +2024,7 @@
         <v>0.1249974336716362</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0.1053416320970148</v>
+        <v>0.1133634178767112</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>0.004077471967380225</v>
@@ -2055,7 +2103,7 @@
         <v>0.1241018679046092</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>0.1013379192186528</v>
+        <v>0.1092293503322356</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>0.003747148908439231</v>
@@ -2134,7 +2182,7 @@
         <v>0.1250648298912176</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>0.1038285943001639</v>
+        <v>0.112193080515564</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>0.003209098074541155</v>
@@ -2213,7 +2261,7 @@
         <v>0.1284710042879902</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>0.1065765311385731</v>
+        <v>0.1145396135219123</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>0.003864214439444336</v>
@@ -2292,7 +2340,7 @@
         <v>0.1273795809788002</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.1048427403491569</v>
+        <v>0.1126379186077146</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>0.003375663076675776</v>
@@ -2371,7 +2419,7 @@
         <v>0.1306935973794915</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>0.1070131687968914</v>
+        <v>0.11481008192798</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>0.003468312238187469</v>
@@ -2450,7 +2498,7 @@
         <v>0.1373616065961974</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>0.1088188087559476</v>
+        <v>0.1169489133823195</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>0.004383351774619117</v>
@@ -2529,7 +2577,7 @@
         <v>0.1376383919458444</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>0.1114829516962353</v>
+        <v>0.1200463297169476</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>0.002507543882017935</v>
@@ -2608,7 +2656,7 @@
         <v>0.1357137073327654</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>0.1083001397465689</v>
+        <v>0.1167776982623895</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>0.005190476190476191</v>
@@ -2687,7 +2735,7 @@
         <v>0.12878961793308</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>0.100648943156759</v>
+        <v>0.1090719405576581</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>0.003909465020576132</v>
@@ -2766,7 +2814,7 @@
         <v>0.1317536944426887</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>0.101569495672799</v>
+        <v>0.109933212782369</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>0.004160887656033287</v>
@@ -2845,7 +2893,7 @@
         <v>0.1324486410354609</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>0.1093379421534574</v>
+        <v>0.1178292651593704</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>0.004345613279567787</v>
@@ -2924,7 +2972,7 @@
         <v>0.1390621054961291</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>0.1173434615179642</v>
+        <v>0.125918130820391</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>0.005360287924037062</v>
@@ -3003,7 +3051,7 @@
         <v>0.1407662015523402</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>0.1196898229738855</v>
+        <v>0.1281805675359595</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>0.005523166615526235</v>
@@ -3082,7 +3130,7 @@
         <v>0.1447913363380809</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>0.1237794516577133</v>
+        <v>0.1321880766766879</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>0.004507512520868113</v>
@@ -3161,7 +3209,7 @@
         <v>0.1451570905231576</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>0.1240245622759706</v>
+        <v>0.132211106034551</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>0.004748417194268577</v>
@@ -3238,7 +3286,7 @@
         <v>0.152824511992362</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>0.1305863598053104</v>
+        <v>0.1382699206781391</v>
       </c>
       <c r="F34" s="9" t="n">
         <v>0.00569764497341099</v>
@@ -3313,7 +3361,7 @@
         <v>0.1540458324268429</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>0.1318263570754138</v>
+        <v>0.139834255760751</v>
       </c>
       <c r="F35" s="9" t="n">
         <v>0.006784771956275914</v>
@@ -3386,7 +3434,7 @@
         <v>0.1583426885091907</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>0.1362220245321215</v>
+        <v>0.1441181605539621</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>0.006692261632207389</v>
@@ -3457,7 +3505,7 @@
         <v>0.1590558927494345</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>0.1368485535724104</v>
+        <v>0.1446940965553226</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>0.007178548807094095</v>
@@ -3526,7 +3574,7 @@
         <v>0.1548417411904113</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>0.1324128596333872</v>
+        <v>0.1405464945747171</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>0.007344672476806298</v>
@@ -3593,7 +3641,7 @@
         <v>0.1489021097958185</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>0.1262286285572796</v>
+        <v>0.1343326096689979</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>0.006071346526205244</v>
@@ -3658,7 +3706,7 @@
         <v>0.1521364582846645</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>0.138363610456143</v>
+        <v>0.1469473839393374</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>0.009204171624553789</v>
@@ -3721,7 +3769,7 @@
         <v>0.150458515523858</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>0.1466626469836667</v>
+        <v>0.1559758940075507</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>0.007134894091415831</v>
@@ -3782,7 +3830,7 @@
         <v>0.1462031928228654</v>
       </c>
       <c r="E42" s="9" t="n">
-        <v>0.1462920637695218</v>
+        <v>0.1556385265325337</v>
       </c>
       <c r="F42" s="9" t="n"/>
       <c r="G42" s="9" t="n"/>
@@ -3833,7 +3881,7 @@
         <v>0.1456686615698962</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>0.144518745947101</v>
+        <v>0.1540494970601763</v>
       </c>
       <c r="F43" s="9" t="n"/>
       <c r="G43" s="9" t="n"/>
@@ -4060,7 +4108,7 @@
         <v>0.1647831307910926</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>0.1358394129528923</v>
+        <v>0.1482142134427212</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>0.002662609357170026</v>
@@ -4139,7 +4187,7 @@
         <v>0.168761002563152</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.1398636726498544</v>
+        <v>0.1520801098576061</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>0.001231375446373599</v>
@@ -4218,7 +4266,7 @@
         <v>0.1601054643738731</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.1310458389197806</v>
+        <v>0.1434557997039363</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0.001351873310158362</v>
@@ -4297,7 +4345,7 @@
         <v>0.1574975375662802</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.1281975853169891</v>
+        <v>0.1404453520941455</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>0.0006750675067506751</v>
@@ -4376,7 +4424,7 @@
         <v>0.1244707638203963</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.1237079702720396</v>
+        <v>0.1355928485890392</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>0</v>
@@ -4455,7 +4503,7 @@
         <v>0.1313883459050301</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.1321812940917224</v>
+        <v>0.144086120071029</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>0.001443522194153735</v>
@@ -4534,7 +4582,7 @@
         <v>0.1176973107058144</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>0.1209246446737693</v>
+        <v>0.132861648083732</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>0.0008644910309055544</v>
@@ -4613,7 +4661,7 @@
         <v>0.122354198654347</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0.1128741749359049</v>
+        <v>0.1240032120415133</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>0.0009940357852882703</v>
@@ -4692,7 +4740,7 @@
         <v>0.1227728550520388</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>0.1076346203964566</v>
+        <v>0.1184391015325355</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>0.001774937877174299</v>
@@ -4771,7 +4819,7 @@
         <v>0.12630418701634</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>0.1088034780041539</v>
+        <v>0.1193567802467971</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>0.0009502090459901178</v>
@@ -4850,7 +4898,7 @@
         <v>0.1164418900467493</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>0.102442549138361</v>
+        <v>0.1126640278640784</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>0.001231337540403263</v>
@@ -4929,7 +4977,7 @@
         <v>0.1181190409820631</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.104045703881591</v>
+        <v>0.1143037902479842</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>0.001134705786999514</v>
@@ -5008,7 +5056,7 @@
         <v>0.1129354456675613</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>0.09658855283424966</v>
+        <v>0.1069382035457842</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>0.002040816326530612</v>
@@ -5087,7 +5135,7 @@
         <v>0.1183286460044823</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0.09822472212819261</v>
+        <v>0.1080511914421464</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>0.0009473060982830077</v>
@@ -5166,7 +5214,7 @@
         <v>0.1194296178288019</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>0.09630346266618714</v>
+        <v>0.106080371433865</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>0.001078894133513149</v>
@@ -5245,7 +5293,7 @@
         <v>0.1200416598918784</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>0.09843435339365381</v>
+        <v>0.1084221756137535</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>0.0006590220113351786</v>
@@ -5324,7 +5372,7 @@
         <v>0.1210744478358421</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>0.09879237774824336</v>
+        <v>0.1084625591766413</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>0.001443174984966927</v>
@@ -5403,7 +5451,7 @@
         <v>0.1244794090125384</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.1017213595106226</v>
+        <v>0.1111127819730546</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>0.0009539384028345599</v>
@@ -5482,7 +5530,7 @@
         <v>0.1234626842908238</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>0.09936809751794384</v>
+        <v>0.1087592585635862</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>0.0006532532009406846</v>
@@ -5561,7 +5609,7 @@
         <v>0.129862556413161</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>0.1007122175076962</v>
+        <v>0.1100945863218348</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>0.001221830029866956</v>
@@ -5640,7 +5688,7 @@
         <v>0.1227789046990485</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>0.09601078422992051</v>
+        <v>0.1056787676952148</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>0.0009946007388462632</v>
@@ -5719,7 +5767,7 @@
         <v>0.1226780994355779</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>0.09483760110163331</v>
+        <v>0.1042979563911636</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>0.0009637006103437199</v>
@@ -5798,7 +5846,7 @@
         <v>0.1176441061625953</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>0.0888431666720744</v>
+        <v>0.0983787191002697</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>0.001097333479644464</v>
@@ -5877,7 +5925,7 @@
         <v>0.1228493377117131</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>0.09215959641415512</v>
+        <v>0.1016207527807161</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>0.0008061265618702137</v>
@@ -5956,7 +6004,7 @@
         <v>0.1080252523173347</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>0.08366964785963384</v>
+        <v>0.09291131980006639</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>0.000912512832211703</v>
@@ -6035,7 +6083,7 @@
         <v>0.1163473425221604</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>0.09321814272898071</v>
+        <v>0.1027096750840385</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>0.001081081081081081</v>
@@ -6114,7 +6162,7 @@
         <v>0.1195117928897177</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>0.09706247940403194</v>
+        <v>0.1067626511002808</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>0.000605052185751021</v>
@@ -6193,7 +6241,7 @@
         <v>0.1173759719083341</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>0.09459688593079311</v>
+        <v>0.104222358899196</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>0.0006838775859121217</v>
@@ -6272,7 +6320,7 @@
         <v>0.1138194687279466</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>0.09079712293049866</v>
+        <v>0.1005176123665087</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>0.0006890611541774332</v>
@@ -6349,7 +6397,7 @@
         <v>0.1142219777757838</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>0.09012107314780494</v>
+        <v>0.09959088877956652</v>
       </c>
       <c r="F34" s="9" t="n">
         <v>0.0005579319323042589</v>
@@ -6424,7 +6472,7 @@
         <v>0.1247723815160504</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>0.1009405062537471</v>
+        <v>0.110657024620381</v>
       </c>
       <c r="F35" s="9" t="n">
         <v>0.0008279287981233614</v>
@@ -6497,7 +6545,7 @@
         <v>0.1256472975073649</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>0.1017849182684195</v>
+        <v>0.1116327400855942</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>0.0006829668078131403</v>
@@ -6568,7 +6616,7 @@
         <v>0.1285042018014208</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>0.1046235447583473</v>
+        <v>0.1142266607108015</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>0.0008762047815746651</v>
@@ -6637,7 +6685,7 @@
         <v>0.1277707998629303</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>0.1037934017058586</v>
+        <v>0.1137515630994501</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>0.0009258187709755816</v>
@@ -6704,7 +6752,7 @@
         <v>0.1295923693386644</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>0.1057573485092276</v>
+        <v>0.1153974652002644</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>0.001578605255826911</v>
@@ -6769,7 +6817,7 @@
         <v>0.1382925912086581</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>0.1229556623779938</v>
+        <v>0.1330338800805461</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>0.00334777471445451</v>
@@ -6832,7 +6880,7 @@
         <v>0.136140821811199</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>0.1303223847064506</v>
+        <v>0.1411487437223177</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>0.001613668723303275</v>
@@ -6893,7 +6941,7 @@
         <v>0.1321783871188548</v>
       </c>
       <c r="E42" s="9" t="n">
-        <v>0.1298423755300882</v>
+        <v>0.1407362905704298</v>
       </c>
       <c r="F42" s="9" t="n"/>
       <c r="G42" s="9" t="n"/>
@@ -6944,7 +6992,7 @@
         <v>0.1291630102006661</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>0.1253490293463322</v>
+        <v>0.1363923855494879</v>
       </c>
       <c r="F43" s="9" t="n"/>
       <c r="G43" s="9" t="n"/>
@@ -7171,7 +7219,7 @@
         <v>0.1760068872662508</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>0.1475899190124463</v>
+        <v>0.1602644708199183</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>0.007390745501285347</v>
@@ -7250,7 +7298,7 @@
         <v>0.1840185172416542</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.1555811003802445</v>
+        <v>0.1681283606053978</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>0.004636233951497861</v>
@@ -7329,7 +7377,7 @@
         <v>0.1846665765755477</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.1562246531073865</v>
+        <v>0.1687419594247823</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0.007893226176808266</v>
@@ -7408,7 +7456,7 @@
         <v>0.1795061581053794</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.1513875282772784</v>
+        <v>0.1634776971071958</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>0.005707537886242866</v>
@@ -7487,7 +7535,7 @@
         <v>0.1441238007611992</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.1472092407870039</v>
+        <v>0.158671499324147</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>0.004731488052992667</v>
@@ -7566,7 +7614,7 @@
         <v>0.137055326255005</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.1388772576201529</v>
+        <v>0.1510084467813982</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>0.005456132693147098</v>
@@ -7645,7 +7693,7 @@
         <v>0.1287980958535307</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>0.1348273495928165</v>
+        <v>0.1465862139884745</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>0.003369272237196766</v>
@@ -7724,7 +7772,7 @@
         <v>0.135658197774737</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0.128279144096289</v>
+        <v>0.1396058948902391</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>0.004248432126239126</v>
@@ -7803,7 +7851,7 @@
         <v>0.1377022733786597</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>0.1239659980452269</v>
+        <v>0.1349472684729881</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>0.004113533525298231</v>
@@ -7882,7 +7930,7 @@
         <v>0.1402034707652893</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>0.1236025810264263</v>
+        <v>0.1343966976840277</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>0.003487894952810833</v>
@@ -7961,7 +8009,7 @@
         <v>0.1323755219088188</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>0.1201887635236014</v>
+        <v>0.130706156527466</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>0.004245283018867924</v>
@@ -8040,7 +8088,7 @@
         <v>0.1322124503128397</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.1198290071587663</v>
+        <v>0.1300399619373314</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>0.00495458298926507</v>
@@ -8119,7 +8167,7 @@
         <v>0.1155471582198858</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>0.09979267698276313</v>
+        <v>0.1096537855984829</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>0.005007363770250369</v>
@@ -8198,7 +8246,7 @@
         <v>0.1339972401767495</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0.1153032213445806</v>
+        <v>0.1251604749587826</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>0.001986316486426837</v>
@@ -8277,7 +8325,7 @@
         <v>0.1291135111651291</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>0.1067934372009991</v>
+        <v>0.1163417424372911</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>0.004396112910689496</v>
@@ -8356,7 +8404,7 @@
         <v>0.1283053076959474</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>0.1072190501605765</v>
+        <v>0.1171080534807934</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>0.003680078508341512</v>
@@ -8435,7 +8483,7 @@
         <v>0.1277131465878496</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>0.1057372146275087</v>
+        <v>0.1154961122821912</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>0.002748625687156422</v>
@@ -8514,7 +8562,7 @@
         <v>0.1284062321397528</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.1059417818987717</v>
+        <v>0.1157391450022276</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>0.00267639902676399</v>
@@ -8593,7 +8641,7 @@
         <v>0.1460842223831064</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>0.12325856508603</v>
+        <v>0.1329185362491287</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>0.0019228128004395</v>
@@ -8672,7 +8720,7 @@
         <v>0.156086815290265</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>0.1274965148996195</v>
+        <v>0.1371768315518572</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>0.00363460140537921</v>
@@ -8751,7 +8799,7 @@
         <v>0.156549002391863</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>0.1309622260888014</v>
+        <v>0.1402426113808196</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>0.003041459900752361</v>
@@ -8830,7 +8878,7 @@
         <v>0.1572351762573019</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>0.1300985053696513</v>
+        <v>0.1396505587252026</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>0.005274261603375527</v>
@@ -8909,7 +8957,7 @@
         <v>0.1527630555308201</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>0.1247880157671762</v>
+        <v>0.1343225181466768</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>0.004680415386865584</v>
@@ -8988,7 +9036,7 @@
         <v>0.1522651514493234</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>0.1220272934157805</v>
+        <v>0.1314586340892016</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>0.00421274354923644</v>
@@ -9067,7 +9115,7 @@
         <v>0.1651060511172867</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>0.1435036749466387</v>
+        <v>0.1525234813264293</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>0.005279831045406547</v>
@@ -9146,7 +9194,7 @@
         <v>0.1679493639012578</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>0.1477035300052429</v>
+        <v>0.1565749792514327</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>0.008671047827674333</v>
@@ -9225,7 +9273,7 @@
         <v>0.1720280487376216</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>0.1526004916187438</v>
+        <v>0.161289271177778</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>0.007797731568998109</v>
@@ -9304,7 +9352,7 @@
         <v>0.1764780845798306</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>0.1572788747009781</v>
+        <v>0.1660701773925423</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>0.005962436649110604</v>
@@ -9383,7 +9431,7 @@
         <v>0.1810039592733451</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>0.1618231392008733</v>
+        <v>0.1702064248435337</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>0.005512220488819553</v>
@@ -9460,7 +9508,7 @@
         <v>0.1958707602630508</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>0.1754676771288392</v>
+        <v>0.1830875396918088</v>
       </c>
       <c r="F34" s="9" t="n">
         <v>0.007606787595084845</v>
@@ -9535,7 +9583,7 @@
         <v>0.1927477924523951</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>0.1722315344843431</v>
+        <v>0.1801763929761666</v>
       </c>
       <c r="F35" s="9" t="n">
         <v>0.01019184652278178</v>
@@ -9608,7 +9656,7 @@
         <v>0.1974858082552343</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>0.177126093992667</v>
+        <v>0.184815317813568</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>0.01098901098901099</v>
@@ -9679,7 +9727,7 @@
         <v>0.1999500578971476</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>0.1795834168636766</v>
+        <v>0.1870015309134935</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>0.01252333540759179</v>
@@ -9748,7 +9796,7 @@
         <v>0.1967993320876152</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>0.1763527003911408</v>
+        <v>0.1840396905312377</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>0.01274800251369064</v>
@@ -9815,7 +9863,7 @@
         <v>0.1881928463842645</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>0.1673016660613234</v>
+        <v>0.1752730737658528</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>0.01005896635449185</v>
@@ -9880,7 +9928,7 @@
         <v>0.1887110782136452</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>0.1783824245788371</v>
+        <v>0.1867871967528555</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>0.01597228904070047</v>
@@ -9943,7 +9991,7 @@
         <v>0.1866387202038333</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>0.1879448204320203</v>
+        <v>0.19724348728017</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>0.01296551724137931</v>
@@ -10004,7 +10052,7 @@
         <v>0.1792801283472147</v>
       </c>
       <c r="E42" s="9" t="n">
-        <v>0.1851156421215646</v>
+        <v>0.1944730451571662</v>
       </c>
       <c r="F42" s="9" t="n"/>
       <c r="G42" s="9" t="n"/>
@@ -10055,7 +10103,7 @@
         <v>0.1812530223447609</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>0.1859482666691393</v>
+        <v>0.1952833044601036</v>
       </c>
       <c r="F43" s="9" t="n"/>
       <c r="G43" s="9" t="n"/>
@@ -10282,7 +10330,7 @@
         <v>0.2007129903743641</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>0.1736127821020439</v>
+        <v>0.1855136495857377</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>0.01050175029171529</v>
@@ -10361,7 +10409,7 @@
         <v>0.1950328371673822</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.167726191661055</v>
+        <v>0.1803088582691409</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>0.01806451612903226</v>
@@ -10440,7 +10488,7 @@
         <v>0.1917378086040138</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.1637568253580393</v>
+        <v>0.1757095237365085</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0.01183431952662722</v>
@@ -10519,7 +10567,7 @@
         <v>0.1604963214547955</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.1311315402447217</v>
+        <v>0.1443129554265116</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>0.007614213197969543</v>
@@ -10598,7 +10646,7 @@
         <v>0.1248604846906471</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.1249818664243621</v>
+        <v>0.1376937354722226</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>0.005830903790087463</v>
@@ -10677,7 +10725,7 @@
         <v>0.1268258089966634</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.1267662613191632</v>
+        <v>0.138750962329447</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>0.01176470588235294</v>
@@ -10756,7 +10804,7 @@
         <v>0.1134870259165308</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>0.1167485940472008</v>
+        <v>0.1296890251659456</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>0.01223241590214067</v>
@@ -10835,7 +10883,7 @@
         <v>0.1255146142084466</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0.1173166929567017</v>
+        <v>0.1288355055500983</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>0.005830903790087463</v>
@@ -10914,7 +10962,7 @@
         <v>0.1253457211311264</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>0.1110283762692514</v>
+        <v>0.1229117330192353</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>0</v>
@@ -10993,7 +11041,7 @@
         <v>0.1324658064721999</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>0.1162578726381399</v>
+        <v>0.1266235674840024</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>0.005681818181818182</v>
@@ -11072,7 +11120,7 @@
         <v>0.1112614252254807</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>0.09744055556354669</v>
+        <v>0.1078684476918524</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>0</v>
@@ -11151,7 +11199,7 @@
         <v>0.1331173022303523</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.1206304259122283</v>
+        <v>0.1321101382843682</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>0</v>
@@ -11230,7 +11278,7 @@
         <v>0.1118519710914956</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>0.09537023226264356</v>
+        <v>0.1068271585047845</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>0</v>
@@ -11309,7 +11357,7 @@
         <v>0.1253252647804549</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0.1055664121910538</v>
+        <v>0.1158155805058365</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>0</v>
@@ -11388,7 +11436,7 @@
         <v>0.1198927255369458</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>0.09634364340078612</v>
+        <v>0.1063030318891025</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>0.007905138339920948</v>
@@ -11467,7 +11515,7 @@
         <v>0.1249429710227454</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>0.1030421841404095</v>
+        <v>0.1137847787506631</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>0</v>
@@ -11546,7 +11594,7 @@
         <v>0.1155406861437549</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>0.09299246547549113</v>
+        <v>0.103237214586798</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>0</v>
@@ -11625,7 +11673,7 @@
         <v>0.1250812496612037</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.1028290119247325</v>
+        <v>0.11239157634579</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>0</v>
@@ -11704,7 +11752,7 @@
         <v>0.1129507094449481</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>0.0889606579346703</v>
+        <v>0.09840940869471689</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>0.004201680672268907</v>
@@ -11783,7 +11831,7 @@
         <v>0.1508943020577949</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>0.1220486696296397</v>
+        <v>0.1314954270842089</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>0.005415162454873646</v>
@@ -11862,7 +11910,7 @@
         <v>0.1507212935992684</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>0.1243062045080212</v>
+        <v>0.1338165828972256</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>0.001639344262295082</v>
@@ -11941,7 +11989,7 @@
         <v>0.145720982291879</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>0.1182340998534005</v>
+        <v>0.1279229161324979</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>0.007692307692307693</v>
@@ -12020,7 +12068,7 @@
         <v>0.1334630320175305</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>0.105582158048375</v>
+        <v>0.1152732495779208</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>0.00535475234270415</v>
@@ -12099,7 +12147,7 @@
         <v>0.1388121667866674</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>0.108796379493882</v>
+        <v>0.1179303955207103</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>0.003210272873194221</v>
@@ -12178,7 +12226,7 @@
         <v>0.1393151821844556</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>0.1162011730603047</v>
+        <v>0.1256236800829641</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>0.008888888888888889</v>
@@ -12257,7 +12305,7 @@
         <v>0.1455616525346343</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>0.1241842120709632</v>
+        <v>0.1336271891791877</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>0.005639097744360902</v>
@@ -12336,7 +12384,7 @@
         <v>0.1332402163723539</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>0.1117658312062143</v>
+        <v>0.1211816008054281</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>0.002109704641350211</v>
@@ -12415,7 +12463,7 @@
         <v>0.1319383195565887</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>0.1104347134438877</v>
+        <v>0.1193586070978649</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>0.00423728813559322</v>
@@ -12494,7 +12542,7 @@
         <v>0.1354317862209026</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>0.1140180347120785</v>
+        <v>0.1233004515904792</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>0.003868471953578337</v>
@@ -12571,7 +12619,7 @@
         <v>0.1432548675197855</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>0.1210670550059376</v>
+        <v>0.1303381080038013</v>
       </c>
       <c r="F34" s="9" t="n">
         <v>0.003883495145631068</v>
@@ -12646,7 +12694,7 @@
         <v>0.1460980776946432</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>0.1242813320355281</v>
+        <v>0.1333446424105137</v>
       </c>
       <c r="F35" s="9" t="n">
         <v>0</v>
@@ -12719,7 +12767,7 @@
         <v>0.1373164778536496</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>0.1149950280816063</v>
+        <v>0.1239156509337488</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>0</v>
@@ -12790,7 +12838,7 @@
         <v>0.1345292527621496</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>0.1118388687689553</v>
+        <v>0.1212090890384997</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>0.002604166666666667</v>
@@ -12859,7 +12907,7 @@
         <v>0.1427772083826232</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>0.1201829011472376</v>
+        <v>0.1295586654654307</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>0.001754385964912281</v>
@@ -12926,7 +12974,7 @@
         <v>0.1477371734413175</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>0.125417004548698</v>
+        <v>0.1346820588449617</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>0.003629764065335753</v>
@@ -12991,7 +13039,7 @@
         <v>0.1444977810946259</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>0.1301520337193116</v>
+        <v>0.1403169354386929</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>0</v>
@@ -13054,7 +13102,7 @@
         <v>0.1439676392249817</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>0.1393779682699878</v>
+        <v>0.1503065184947831</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>0.007971014492753623</v>
@@ -13115,7 +13163,7 @@
         <v>0.1450648113286439</v>
       </c>
       <c r="E42" s="9" t="n">
-        <v>0.1449281231006304</v>
+        <v>0.1555763611469222</v>
       </c>
       <c r="F42" s="9" t="n"/>
       <c r="G42" s="9" t="n"/>
@@ -13166,7 +13214,7 @@
         <v>0.1394301871223121</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>0.137505782185995</v>
+        <v>0.1484764086309239</v>
       </c>
       <c r="F43" s="9" t="n"/>
       <c r="G43" s="9" t="n"/>
@@ -13393,7 +13441,7 @@
         <v>0.1628693777314506</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>0.1339763257067486</v>
+        <v>0.1459371365111581</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>0.00670621614650503</v>
@@ -13472,7 +13520,7 @@
         <v>0.1494665158895451</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.1204308212630295</v>
+        <v>0.1324628455157178</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>0.001223241590214067</v>
@@ -13551,7 +13599,7 @@
         <v>0.1533249359558859</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.1243510207837713</v>
+        <v>0.1360351415500845</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0.002705139765554554</v>
@@ -13630,7 +13678,7 @@
         <v>0.1592472937279113</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.1305084881151846</v>
+        <v>0.1416798243217242</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>0.00749375520399667</v>
@@ -13709,7 +13757,7 @@
         <v>0.1294787542790824</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.1295594844219896</v>
+        <v>0.1406895714117863</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>0.004016064257028112</v>
@@ -13788,7 +13836,7 @@
         <v>0.133311817776777</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.1343879396729252</v>
+        <v>0.1450418798271424</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>0.005882352941176471</v>
@@ -13867,7 +13915,7 @@
         <v>0.1233243359197484</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>0.1281700874969506</v>
+        <v>0.1392136124024488</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>0.00396039603960396</v>
@@ -13946,7 +13994,7 @@
         <v>0.1267958915928095</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0.1179493095925534</v>
+        <v>0.1289180149305124</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>0.002649006622516556</v>
@@ -14025,7 +14073,7 @@
         <v>0.1277298057352472</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>0.1128041705791211</v>
+        <v>0.1236730696914808</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>0.003101736972704715</v>
@@ -14104,7 +14152,7 @@
         <v>0.1363159760616384</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>0.1191440936874586</v>
+        <v>0.1295763697219605</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>0.009124087591240875</v>
@@ -14183,7 +14231,7 @@
         <v>0.134978393757888</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>0.1229881236818814</v>
+        <v>0.1325203654919286</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>0.01058574453069866</v>
@@ -14262,7 +14310,7 @@
         <v>0.1285060639208936</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.1159007711429499</v>
+        <v>0.1261044400950595</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>0.01483171705647461</v>
@@ -14341,7 +14389,7 @@
         <v>0.1355957553755318</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>0.1215761570048713</v>
+        <v>0.1306912355050515</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>0.01377410468319559</v>
@@ -14420,7 +14468,7 @@
         <v>0.1365236835393159</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0.1171732903505085</v>
+        <v>0.1264718655342855</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>0.006000705965407695</v>
@@ -14499,7 +14547,7 @@
         <v>0.1367166246482283</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>0.1139823188666638</v>
+        <v>0.1233939720483078</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>0.006056287851799074</v>
@@ -14578,7 +14626,7 @@
         <v>0.1371088256330188</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>0.1163400586953284</v>
+        <v>0.1252127974549112</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>0.007676902536715621</v>
@@ -14657,7 +14705,7 @@
         <v>0.1467351696555365</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>0.1257605032206868</v>
+        <v>0.1344701612421309</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>0.005702950657079098</v>
@@ -14736,7 +14784,7 @@
         <v>0.1469596996971839</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.1252860371943297</v>
+        <v>0.1341824119072631</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>0.007640317367029092</v>
@@ -14815,7 +14863,7 @@
         <v>0.1416035166912635</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>0.1180707909146485</v>
+        <v>0.126991584548249</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>0.007859949982136478</v>
@@ -14894,7 +14942,7 @@
         <v>0.1472390637211843</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>0.117932881001882</v>
+        <v>0.1269625066397997</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>0.008846657929226736</v>
@@ -14973,7 +15021,7 @@
         <v>0.1538517398523786</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>0.1271090875621042</v>
+        <v>0.1365564204463591</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>0.00337193959829937</v>
@@ -15052,7 +15100,7 @@
         <v>0.1483420271596743</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>0.1200706709364847</v>
+        <v>0.1296399062026055</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>0.01017728168089297</v>
@@ -15131,7 +15179,7 @@
         <v>0.1454304518319132</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>0.1164342793513876</v>
+        <v>0.1259666205795335</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>0.008088070096607504</v>
@@ -15210,7 +15258,7 @@
         <v>0.14823869999618</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>0.1170420609748146</v>
+        <v>0.1264723181968003</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>0.009675967596759675</v>
@@ -15289,7 +15337,7 @@
         <v>0.1424779711483818</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>0.1190676525163786</v>
+        <v>0.1286166763915489</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>0.009222919937205651</v>
@@ -15368,7 +15416,7 @@
         <v>0.1370534886507126</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>0.1146923905608326</v>
+        <v>0.1241257803236423</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>0.006622516556291391</v>
@@ -15447,7 +15495,7 @@
         <v>0.141226058658709</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>0.1195892233444783</v>
+        <v>0.1291616962109224</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>0.009948269001193792</v>
@@ -15526,7 +15574,7 @@
         <v>0.1414175864677958</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>0.119526929250212</v>
+        <v>0.1288031711899578</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>0.006958811359789355</v>
@@ -15605,7 +15653,7 @@
         <v>0.1446781351789757</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>0.1231068542942323</v>
+        <v>0.1324306078089289</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>0.008435428800964049</v>
@@ -15682,7 +15730,7 @@
         <v>0.1437041214350047</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>0.1204607183077246</v>
+        <v>0.129538765487403</v>
       </c>
       <c r="F34" s="9" t="n">
         <v>0.007791629563668744</v>
@@ -15757,7 +15805,7 @@
         <v>0.1419560941322973</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>0.1185520657831605</v>
+        <v>0.1278408406085113</v>
       </c>
       <c r="F35" s="9" t="n">
         <v>0.009426751592356689</v>
@@ -15830,7 +15878,7 @@
         <v>0.1397950623310689</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>0.1162028234761349</v>
+        <v>0.1253150062107966</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>0.005648197955890263</v>
@@ -15901,7 +15949,7 @@
         <v>0.1405844445805216</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>0.1171527356709832</v>
+        <v>0.1262769612655364</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>0.005511622334052241</v>
@@ -15970,7 +16018,7 @@
         <v>0.1464657426648131</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>0.1231724004780741</v>
+        <v>0.132373986501076</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>0.008089607965152458</v>
@@ -16037,7 +16085,7 @@
         <v>0.141885627445472</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>0.1183773037538525</v>
+        <v>0.1273734036213583</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>0.005937921727395412</v>
@@ -16102,7 +16150,7 @@
         <v>0.1463857051387521</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>0.1317730448755334</v>
+        <v>0.141431625604583</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>0.00823045267489712</v>
@@ -16165,7 +16213,7 @@
         <v>0.1489306789673813</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>0.1449081079485941</v>
+        <v>0.1550350998910636</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>0.006918819188191882</v>
@@ -16226,7 +16274,7 @@
         <v>0.1384608891487341</v>
       </c>
       <c r="E42" s="9" t="n">
-        <v>0.1370755575833351</v>
+        <v>0.1471590768828682</v>
       </c>
       <c r="F42" s="9" t="n"/>
       <c r="G42" s="9" t="n"/>
@@ -16277,7 +16325,7 @@
         <v>0.1373976157006845</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>0.1345656123348273</v>
+        <v>0.145038916232958</v>
       </c>
       <c r="F43" s="9" t="n"/>
       <c r="G43" s="9" t="n"/>
@@ -30724,7 +30772,7 @@
         <v>0.1697302748267528</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>0.1410547877378319</v>
+        <v>0.1534218648848316</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>0.005412576280180419</v>
@@ -30803,7 +30851,7 @@
         <v>0.1729214610076629</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.1442500576370642</v>
+        <v>0.1565862188532028</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>0.003255904363883759</v>
@@ -30882,7 +30930,7 @@
         <v>0.1706303560993175</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.141900067921762</v>
+        <v>0.1541876684699905</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0.004891943773608273</v>
@@ -30961,7 +31009,7 @@
         <v>0.1670105832696708</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.1383051144902723</v>
+        <v>0.1503078943403029</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>0.004301598896193491</v>
@@ -31040,7 +31088,7 @@
         <v>0.1330364946297469</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.1339545002273516</v>
+        <v>0.1455767905193738</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>0.002701947265443026</v>
@@ -31119,7 +31167,7 @@
         <v>0.133669299163202</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.1348673005519391</v>
+        <v>0.146701299309117</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>0.00383525095881274</v>
@@ -31198,7 +31246,7 @@
         <v>0.1228771363216597</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>0.1274722245310928</v>
+        <v>0.1392427071128185</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>0.00265543448402161</v>
@@ -31277,7 +31325,7 @@
         <v>0.1285737696440496</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0.1200899706041318</v>
+        <v>0.1312924806325065</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>0.002705902249281245</v>
@@ -31356,7 +31404,7 @@
         <v>0.1293322652446746</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>0.1147906667124662</v>
+        <v>0.1256980890682544</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>0.00282303597354412</v>
@@ -31435,7 +31483,7 @@
         <v>0.13342365455931</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>0.1163665135485878</v>
+        <v>0.1269947189043743</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>0.003214638971315529</v>
@@ -31514,7 +31562,7 @@
         <v>0.1251508938534342</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>0.1121450872226465</v>
+        <v>0.1224323288920566</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>0.003445661911653229</v>
@@ -31593,7 +31641,7 @@
         <v>0.125680453106082</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.1125368524408116</v>
+        <v>0.1227929095606655</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>0.004416403785488959</v>
@@ -31672,7 +31720,7 @@
         <v>0.1173323917087008</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>0.1015338803574728</v>
+        <v>0.1115609316890239</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>0.004772425983208131</v>
@@ -31751,7 +31799,7 @@
         <v>0.1260661151562001</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0.1064977500066081</v>
+        <v>0.1162477883052176</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>0.002111145606954362</v>
@@ -31830,7 +31878,7 @@
         <v>0.1255454238294707</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>0.1027218167257971</v>
+        <v>0.1123657843889724</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>0.00310873825775495</v>
@@ -31909,7 +31957,7 @@
         <v>0.1258153246818414</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>0.1045158286872714</v>
+        <v>0.1142622723152918</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>0.002892700975445678</v>
@@ -31988,7 +32036,7 @@
         <v>0.1288403343870299</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>0.1069464066695982</v>
+        <v>0.1164124240128303</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>0.002774092389337836</v>
@@ -32067,7 +32115,7 @@
         <v>0.1306398721063738</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.1082139759419328</v>
+        <v>0.1176066731372975</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>0.002922034798778058</v>
@@ -32146,7 +32194,7 @@
         <v>0.1353134387269145</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>0.1118218234560582</v>
+        <v>0.1212493941628916</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>0.002336968617849989</v>
@@ -32225,7 +32273,7 @@
         <v>0.1444854483388257</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>0.1155595830612563</v>
+        <v>0.1250157249217198</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>0.003588890044731093</v>
@@ -32304,7 +32352,7 @@
         <v>0.1440163282410938</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>0.1176232282679054</v>
+        <v>0.1270970370615382</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>0.002413593357791079</v>
@@ -32383,7 +32431,7 @@
         <v>0.1423740726484915</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>0.1146179133256061</v>
+        <v>0.1241486386427458</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>0.005505775666630681</v>
@@ -32462,7 +32510,7 @@
         <v>0.135404746365845</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>0.1068622229590486</v>
+        <v>0.1164022540837809</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>0.003877435218460375</v>
@@ -32541,7 +32589,7 @@
         <v>0.1387968886190033</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>0.1081478788431385</v>
+        <v>0.11758096994722</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>0.004119294776734223</v>
@@ -32620,7 +32668,7 @@
         <v>0.1376506547714917</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>0.1145578324181424</v>
+        <v>0.1237907176176086</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>0.004596504921729327</v>
@@ -32699,7 +32747,7 @@
         <v>0.1441963469977625</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>0.1225595558850763</v>
+        <v>0.1317557132179211</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>0.005609041439933026</v>
@@ -32778,7 +32826,7 @@
         <v>0.1467361312606717</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>0.1257508166669354</v>
+        <v>0.1349971830673408</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>0.005880923450789793</v>
@@ -32857,7 +32905,7 @@
         <v>0.1509895036587559</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>0.1301158642225724</v>
+        <v>0.1392536978051587</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>0.004746325054144971</v>
@@ -32936,7 +32984,7 @@
         <v>0.1525839430537038</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>0.131712714357672</v>
+        <v>0.1407132264491822</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>0.004828839166188563</v>
@@ -33013,7 +33061,7 @@
         <v>0.1619306871061364</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>0.1399014270550064</v>
+        <v>0.1483618616706517</v>
       </c>
       <c r="F34" s="9" t="n">
         <v>0.005717608295377459</v>
@@ -33088,7 +33136,7 @@
         <v>0.1620798449778373</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>0.1400216171219286</v>
+        <v>0.1487668844985111</v>
       </c>
       <c r="F35" s="9" t="n">
         <v>0.006924852526288792</v>
@@ -33161,7 +33209,7 @@
         <v>0.1671436943860002</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>0.1452574007575879</v>
+        <v>0.1538036629825614</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>0.007033857892226991</v>
@@ -33232,7 +33280,7 @@
         <v>0.1667386872219692</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>0.1447282260387432</v>
+        <v>0.1531433164079337</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>0.007558459963782379</v>
@@ -33301,7 +33349,7 @@
         <v>0.162238671324329</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>0.1399860915401042</v>
+        <v>0.1487810892617213</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>0.007548369154979937</v>
@@ -33368,7 +33416,7 @@
         <v>0.1571303069685226</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>0.1346506148672444</v>
+        <v>0.1434684890706845</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>0.005911812328199722</v>
@@ -33433,7 +33481,7 @@
         <v>0.1606724742328915</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>0.1475621816444056</v>
+        <v>0.1568882277536311</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>0.009152950622240065</v>
@@ -33496,7 +33544,7 @@
         <v>0.1588283715302923</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>0.1562157854957739</v>
+        <v>0.1663230895796254</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>0.007336135073361351</v>
@@ -33557,7 +33605,7 @@
         <v>0.1539917064107829</v>
       </c>
       <c r="E42" s="9" t="n">
-        <v>0.1554181398511428</v>
+        <v>0.165520221475138</v>
       </c>
       <c r="F42" s="9" t="n"/>
       <c r="G42" s="9" t="n"/>
@@ -33608,7 +33656,7 @@
         <v>0.1540411035862974</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>0.1542409713933532</v>
+        <v>0.1644306082276787</v>
       </c>
       <c r="F43" s="9" t="n"/>
       <c r="G43" s="9" t="n"/>
@@ -33835,7 +33883,7 @@
         <v>0.1732909724914043</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>0.1448085439824769</v>
+        <v>0.1571700622679238</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>0.007391859828435846</v>
@@ -33914,7 +33962,7 @@
         <v>0.1756337579513791</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.1471096412030216</v>
+        <v>0.1595238532076413</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>0.004575740547483343</v>
@@ -33993,7 +34041,7 @@
         <v>0.1755978056804268</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.1470229553315022</v>
+        <v>0.1592528053281282</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0.006562756357670222</v>
@@ -34072,7 +34120,7 @@
         <v>0.1723775980095297</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.1440075214530844</v>
+        <v>0.1558720860048862</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>0.006347594261774787</v>
@@ -34151,7 +34199,7 @@
         <v>0.1390337273522765</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.1411285319717646</v>
+        <v>0.152566973210975</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>0.004593695548867417</v>
@@ -34230,7 +34278,7 @@
         <v>0.1356285432668579</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.137174468531251</v>
+        <v>0.1489476296466067</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>0.005889646621202728</v>
@@ -34309,7 +34357,7 @@
         <v>0.1266850570595874</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>0.1322856423893444</v>
+        <v>0.1439337080863779</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>0.003972036860502065</v>
@@ -34388,7 +34436,7 @@
         <v>0.1331771307503185</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0.125430678698773</v>
+        <v>0.1366875690687477</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>0.003972925250147146</v>
@@ -34467,7 +34515,7 @@
         <v>0.1347958543968493</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>0.1207512174138851</v>
+        <v>0.1317443835354692</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>0.003696037847427557</v>
@@ -34546,7 +34594,7 @@
         <v>0.1388767314459342</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>0.1221593364066388</v>
+        <v>0.1328449129678636</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>0.004949053857350801</v>
@@ -34625,7 +34673,7 @@
         <v>0.1322113377930439</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>0.1200109956246433</v>
+        <v>0.1303515517244467</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>0.005240828550037434</v>
@@ -34704,7 +34752,7 @@
         <v>0.1314421071813133</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.1190069482241407</v>
+        <v>0.1292614590962301</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>0.00691699604743083</v>
@@ -34783,7 +34831,7 @@
         <v>0.1220893452913871</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>0.1068841151020086</v>
+        <v>0.1165621536728785</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>0.007727690892364305</v>
@@ -34862,7 +34910,7 @@
         <v>0.134596523378949</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0.1156186012380989</v>
+        <v>0.125284375838982</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>0.003394255874673629</v>
@@ -34941,7 +34989,7 @@
         <v>0.1316885695210122</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>0.1091688629669253</v>
+        <v>0.1186792952345591</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>0.005147656461663506</v>
@@ -35020,7 +35068,7 @@
         <v>0.1318341203346924</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>0.1108555034677985</v>
+        <v>0.1203503203607123</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>0.005221214619400934</v>
@@ -35099,7 +35147,7 @@
         <v>0.1366513113645463</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>0.1151477796563002</v>
+        <v>0.1244084474932841</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>0.004112737389621386</v>
@@ -35178,7 +35226,7 @@
         <v>0.136495503995307</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.1143853256016419</v>
+        <v>0.1237792344537759</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>0.004792746113989638</v>
@@ -35257,7 +35305,7 @@
         <v>0.1441044519517486</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>0.1210601272291081</v>
+        <v>0.1305147070023064</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>0.003585966272533437</v>
@@ -35336,7 +35384,7 @@
         <v>0.1535674232059798</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>0.1247809738426664</v>
+        <v>0.1342829346120025</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>0.00505902192242833</v>
@@ -35415,7 +35463,7 @@
         <v>0.1549440213898667</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>0.1287438878043389</v>
+        <v>0.1381177842321906</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>0.003143734464102939</v>
@@ -35494,7 +35542,7 @@
         <v>0.1523437579512233</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>0.1246302892529601</v>
+        <v>0.1341966343905792</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>0.007804878048780488</v>
@@ -35573,7 +35621,7 @@
         <v>0.1488532477511557</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>0.1205063991072161</v>
+        <v>0.1300498215374358</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>0.005982550893228085</v>
@@ -35652,7 +35700,7 @@
         <v>0.1498241667129239</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>0.1192033216263904</v>
+        <v>0.1286170063993093</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>0.00641025641025641</v>
@@ -35731,7 +35779,7 @@
         <v>0.155820929244389</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>0.1335026144262889</v>
+        <v>0.1427301104164329</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>0.006856023506366308</v>
@@ -35810,7 +35858,7 @@
         <v>0.159091493946647</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>0.1382529233456929</v>
+        <v>0.1472910982140388</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>0.008030838419530999</v>
@@ -35889,7 +35937,7 @@
         <v>0.1596249955524489</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>0.1393327844157936</v>
+        <v>0.1483643050119294</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>0.008378688054998567</v>
@@ -35968,7 +36016,7 @@
         <v>0.1633920741361857</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>0.1432214978352785</v>
+        <v>0.1521794044201584</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>0.006245268735806208</v>
@@ -36047,7 +36095,7 @@
         <v>0.1674755963831341</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>0.1474307348880632</v>
+        <v>0.1561546624726035</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>0.006419164846800344</v>
@@ -36124,7 +36172,7 @@
         <v>0.1787401838671158</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>0.1574408388208816</v>
+        <v>0.1655456321467256</v>
       </c>
       <c r="F34" s="9" t="n">
         <v>0.007535548129218268</v>
@@ -36199,7 +36247,7 @@
         <v>0.1788239576741628</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>0.1575617676428744</v>
+        <v>0.1658711239570365</v>
       </c>
       <c r="F35" s="9" t="n">
         <v>0.009661237381556945</v>
@@ -36272,7 +36320,7 @@
         <v>0.1841697057937505</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>0.1630942019851395</v>
+        <v>0.1711064330620714</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>0.009639634590595752</v>
@@ -36343,7 +36391,7 @@
         <v>0.1842804838121468</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>0.1631280594246665</v>
+        <v>0.1709980894145604</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>0.01062424625279963</v>
@@ -36412,7 +36460,7 @@
         <v>0.1802566312334607</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>0.1589056942538196</v>
+        <v>0.1670926522120048</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>0.01101028433151845</v>
@@ -36479,7 +36527,7 @@
         <v>0.1759139432958562</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>0.1543587213664516</v>
+        <v>0.1626157436982848</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>0.008867494299467951</v>
@@ -36544,7 +36592,7 @@
         <v>0.1760777942812929</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>0.1645002194422691</v>
+        <v>0.1733085039477379</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>0.01314897654873255</v>
@@ -36607,7 +36655,7 @@
         <v>0.1732345758754582</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>0.1726576502004646</v>
+        <v>0.182308366754403</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>0.01096980290518956</v>
@@ -36668,7 +36716,7 @@
         <v>0.1672698734027157</v>
       </c>
       <c r="E42" s="9" t="n">
-        <v>0.170986576046314</v>
+        <v>0.1806066541663339</v>
       </c>
       <c r="F42" s="9" t="n"/>
       <c r="G42" s="9" t="n"/>
@@ -36719,7 +36767,7 @@
         <v>0.1676577103942724</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>0.1700544908891963</v>
+        <v>0.1797768587576279</v>
       </c>
       <c r="F43" s="9" t="n"/>
       <c r="G43" s="9" t="n"/>
